--- a/workspaces/nasdaq_hourly_24hrs/time_of_day/time_of_day.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/time_of_day/time_of_day.xlsx
@@ -622,79 +622,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2.701785348657303</v>
+        <v>2.808438972354807</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.327924712220231</v>
+        <v>1.467239583839905</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.7175830366121758</v>
+        <v>-0.5748792128857971</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2196616492532115</v>
+        <v>-0.0782988300177081</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.223447848438262</v>
+        <v>0.1910815828805923</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.006475324505970548</v>
+        <v>0.0879794167907022</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.0410345671879</v>
+        <v>0.1244644086993816</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.092571234446375</v>
+        <v>1.057455772448449</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.08002527057142572</v>
+        <v>-0.1123329573256839</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.663753567711154</v>
+        <v>-1.693285013498219</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.7824859892416711</v>
+        <v>-0.8136361225212809</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.6571891232988776</v>
+        <v>-0.6887411596769013</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.6487088204110805</v>
+        <v>0.7332057715984703</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.427369454321429</v>
+        <v>0.5122543321475206</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>1.308134402495121</v>
+        <v>1.270757074512531</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.2811380626701379</v>
+        <v>0.2467924368077306</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.3499617040550405</v>
+        <v>0.315409789638629</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.2449792290682211</v>
+        <v>0.2105896489261667</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.05520092214812422</v>
+        <v>0.02132805944100369</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.649014599895537</v>
+        <v>0.7339459509595656</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.3083910892937354</v>
+        <v>0.3944929089407125</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.7603089198515605</v>
+        <v>0.7242833434567331</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.8319486460881649</v>
+        <v>0.7963147978127409</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>1.366051025236779</v>
+        <v>1.329299444560299</v>
       </c>
     </row>
     <row r="7">
@@ -704,79 +704,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.2783696464330347</v>
+        <v>0.390578777477991</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.297103312835574</v>
+        <v>-1.354009642080158</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.8984821825842602</v>
+        <v>0.8363200328717824</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-2.44291656453035</v>
+        <v>-2.498732446494373</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.7874699878944611</v>
+        <v>-0.704008599165121</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.207349559890098</v>
+        <v>-1.122334122458184</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.5617584663152968</v>
+        <v>0.5279218058601245</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.08077990863912277</v>
+        <v>0.04803897616153563</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1.293901153712241</v>
+        <v>-1.323743559109118</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.056456843265138</v>
+        <v>-1.087213530175688</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.02741447850428358</v>
+        <v>-0.005380851093129024</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.7608125762507782</v>
+        <v>0.8446799101367901</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.4463931106079357</v>
+        <v>0.5306070793693323</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.9530322771943318</v>
+        <v>0.9160572216128742</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.5167524098488272</v>
+        <v>-0.5497898576194302</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.935308125002976</v>
+        <v>-0.9671811148872891</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-1.678385437883875</v>
+        <v>-1.708827078582352</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.04205660445314408</v>
+        <v>0.008070449406986313</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.5540540318463343</v>
+        <v>-0.4647957746773912</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-1.178910731538792</v>
+        <v>-1.089258185884979</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-1.195363851231335</v>
+        <v>-1.226055607392638</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-1.880788664778834</v>
+        <v>-1.910276315657178</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0.01919931614055059</v>
+        <v>-0.01477809512616091</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-1.682729462568098</v>
+        <v>-1.713296904324089</v>
       </c>
     </row>
     <row r="8">
@@ -786,79 +786,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.7352240512035308</v>
+        <v>0.6432218785715662</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.4459450434889121</v>
+        <v>-0.505879363094742</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.272880662112648</v>
+        <v>-1.331989951954654</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.5564106692269846</v>
+        <v>-0.499935688510611</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1028331695490863</v>
+        <v>-0.02077464033300913</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.4142788768228272</v>
+        <v>-0.4460456394562442</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.6561848467327849</v>
+        <v>0.6203968953749666</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.46545309985337</v>
+        <v>-1.495425591895369</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.014128881875152</v>
+        <v>-1.045916172454348</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.8748269619721754</v>
+        <v>0.8386981169607068</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.53450060735873</v>
+        <v>0.6185839028915794</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.6654592705354716</v>
+        <v>0.7491445947073814</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.3388988332205543</v>
+        <v>-0.3733863077767481</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.5603252365527922</v>
+        <v>-0.5944651842233384</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-1.218890411856286</v>
+        <v>-1.251442582513228</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.2133011050552511</v>
+        <v>-0.2480966436210608</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.8843468457728818</v>
+        <v>0.8472042270949558</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.1633047993974159</v>
+        <v>0.2503720176311219</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.237776134129362</v>
+        <v>-0.1479610574231387</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-1.366631375833585</v>
+        <v>-1.397116579838389</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.4703367205851876</v>
+        <v>-0.5042938758185969</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.6875078940272132</v>
+        <v>0.6501076015101788</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.6829560671140769</v>
+        <v>-0.7169678992431443</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.142028870376997</v>
+        <v>-0.1772126695964147</v>
       </c>
     </row>
     <row r="9">
@@ -871,76 +871,76 @@
         <v>486</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-4.577120786249196</v>
+        <v>-4.665044155328125</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.671360984310354</v>
+        <v>-1.734632732541478</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.04588796458681799</v>
+        <v>0.005579943072703486</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.2614053938278929</v>
+        <v>0.3151208111555448</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.2175113694709907</v>
+        <v>0.1838293161134033</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.6096436872105215</v>
+        <v>0.5752944797158577</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.800617925985286</v>
+        <v>-1.832646024215386</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.25979719349165</v>
+        <v>-1.294576327910988</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.033856793539144</v>
+        <v>0.9985108332844277</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.694496295961585</v>
+        <v>1.779055684299884</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.5344947255350121</v>
+        <v>0.6186890969536023</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.445262673787596</v>
+        <v>-0.4797324376419425</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1337712781044331</v>
+        <v>-0.1684682749898982</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.38083545701739</v>
+        <v>-1.414137315370887</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-1.628582178305216</v>
+        <v>-1.664027807373365</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.6233097523822693</v>
+        <v>-0.6602126201097178</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.1423455640195144</v>
+        <v>-0.05535948655123235</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.2478014723966595</v>
+        <v>-0.1602001903724144</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.5033592144735763</v>
+        <v>0.4663688086217022</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.07323918364525639</v>
+        <v>0.03719819148501813</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.2644342779809534</v>
+        <v>-0.3000091674460919</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.9572772279336164</v>
+        <v>-0.9928281597683295</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.4770183430769208</v>
+        <v>-0.5133530687469019</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.8867777139851398</v>
+        <v>0.9741211876466238</v>
       </c>
     </row>
     <row r="10">
@@ -953,76 +953,76 @@
         <v>486</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.7364863905708603</v>
+        <v>0.6443360061069683</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.393598999531655</v>
+        <v>1.443598992103709</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.9766048325032912</v>
+        <v>1.028074830598285</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.01759947373187</v>
+        <v>1.95111263119643</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1920436014075975</v>
+        <v>-0.2251686388968537</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2089040651563394</v>
+        <v>-0.2427014303045851</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.5698448031356804</v>
+        <v>-0.6056521591847286</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.197532631779922</v>
+        <v>1.161003499864002</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.64678377638112</v>
+        <v>1.732299229188783</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.079743112864243</v>
+        <v>1.164301585939214</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4493001526996565</v>
+        <v>0.4137710641667027</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.400674068339008</v>
+        <v>1.364529857440033</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.5440263883367251</v>
+        <v>-0.5783043405636263</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.5594802208777807</v>
+        <v>-0.5944651842233597</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.4236792244771479</v>
+        <v>0.3861872608899191</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.6080189220979548</v>
+        <v>0.6945740775309446</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.4736704598470922</v>
+        <v>0.5606569405534714</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.08155783771314162</v>
+        <v>0.04513861866247737</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.7096850342729937</v>
+        <v>0.6717076176566366</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.8957199482080185</v>
+        <v>0.8585534276246563</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.2634463978588215</v>
+        <v>-0.3000091674461132</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.481922984319489</v>
+        <v>0.4455839140805651</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>1.166814180194685</v>
+        <v>1.255714757742368</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.3477901872494229</v>
+        <v>-0.2604467135879389</v>
       </c>
     </row>
     <row r="11">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr"/>
@@ -1250,79 +1250,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2927</v>
+        <v>2931</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1750470309459544</v>
+        <v>0.1714199146940913</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.01438268963399025</v>
+        <v>0.02437608821821868</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2224898329845644</v>
+        <v>0.2323387278952609</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1727803361695166</v>
+        <v>0.1827652992560189</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1394737357079521</v>
+        <v>-0.1339178226704476</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1030395225153029</v>
+        <v>-0.09755297071083646</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.2310575188644108</v>
+        <v>0.2167169468923618</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1419956628939829</v>
+        <v>0.127729300746239</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.02056268051775589</v>
+        <v>-0.01507247430370029</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2796645690254778</v>
+        <v>0.2848181771280878</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2336159415805454</v>
+        <v>0.2388036615968048</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3147016125182702</v>
+        <v>0.3198032394167143</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.04089179463143466</v>
+        <v>-0.03520185366723183</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1399228844264897</v>
+        <v>-0.1542399137872863</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.1312420509075949</v>
+        <v>-0.1457443203572097</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.01317776214347788</v>
+        <v>-0.007477772964499252</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.1116489714143256</v>
+        <v>0.1171894343538114</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.1634518676372423</v>
+        <v>0.1689293856896654</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.3659718701473409</v>
+        <v>0.371150369406557</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.006680366403145399</v>
+        <v>-0.00101414312064918</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.1200733749587712</v>
+        <v>-0.1345623560764651</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.1073209028772766</v>
+        <v>-0.1218594932675288</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.0650704630428578</v>
+        <v>0.07069238505890496</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.02463174049077566</v>
+        <v>-0.01888250636923061</v>
       </c>
     </row>
     <row r="7">
@@ -1332,79 +1332,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2927</v>
+        <v>2931</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1750470309459544</v>
+        <v>0.1714199146940913</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.01438268963399025</v>
+        <v>0.02437608821821868</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.2224898329845644</v>
+        <v>0.2323387278952609</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1727803361695166</v>
+        <v>0.1827652992560189</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1394737357079521</v>
+        <v>-0.1339178226704476</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1030395225153029</v>
+        <v>-0.09755297071083646</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.2310575188644108</v>
+        <v>0.2167169468923618</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1419956628939829</v>
+        <v>0.127729300746239</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.02056268051775589</v>
+        <v>-0.01507247430370029</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2796645690254778</v>
+        <v>0.2848181771280878</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2336159415805454</v>
+        <v>0.2388036615968048</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.3147016125182702</v>
+        <v>0.3198032394167143</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.04089179463143466</v>
+        <v>-0.03520185366723183</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1399228844264897</v>
+        <v>-0.1542399137872863</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.1312420509075949</v>
+        <v>-0.1457443203572097</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.01317776214347788</v>
+        <v>-0.007477772964499252</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.1116489714143256</v>
+        <v>0.1171894343538114</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.1634518676372423</v>
+        <v>0.1689293856896654</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.3659718701473409</v>
+        <v>0.371150369406557</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.006680366403145399</v>
+        <v>-0.00101414312064918</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1200733749587712</v>
+        <v>-0.1345623560764651</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.1073209028772766</v>
+        <v>-0.1218594932675288</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0.0650704630428578</v>
+        <v>0.07069238505890496</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.02463174049077566</v>
+        <v>-0.01888250636923061</v>
       </c>
     </row>
     <row r="8">
@@ -1414,79 +1414,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2927</v>
+        <v>2931</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1750470309459544</v>
+        <v>0.1714199146940913</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.01438268963399025</v>
+        <v>0.02437608821821868</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2224898329845644</v>
+        <v>0.2323387278952609</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1727803361695166</v>
+        <v>0.1827652992560189</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1394737357079521</v>
+        <v>-0.1339178226704476</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1030395225153029</v>
+        <v>-0.09755297071083646</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.2310575188644108</v>
+        <v>0.2167169468923618</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1419956628939829</v>
+        <v>0.127729300746239</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.02056268051775589</v>
+        <v>-0.01507247430370029</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2796645690254778</v>
+        <v>0.2848181771280878</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2336159415805454</v>
+        <v>0.2388036615968048</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.3147016125182702</v>
+        <v>0.3198032394167143</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.04089179463143466</v>
+        <v>-0.03520185366723183</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1399228844264897</v>
+        <v>-0.1542399137872863</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.1312420509075949</v>
+        <v>-0.1457443203572097</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.01317776214347788</v>
+        <v>-0.007477772964499252</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.1116489714143256</v>
+        <v>0.1171894343538114</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.1634518676372423</v>
+        <v>0.1689293856896654</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.3659718701473409</v>
+        <v>0.371150369406557</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.006680366403145399</v>
+        <v>-0.00101414312064918</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1200733749587712</v>
+        <v>-0.1345623560764651</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.1073209028772766</v>
+        <v>-0.1218594932675288</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.0650704630428578</v>
+        <v>0.07069238505890496</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.02463174049077566</v>
+        <v>-0.01888250636923061</v>
       </c>
     </row>
     <row r="9">
@@ -1496,79 +1496,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2927</v>
+        <v>2931</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1750470309459544</v>
+        <v>0.1714199146940913</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.01438268963399025</v>
+        <v>0.02437608821821868</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.2224898329845644</v>
+        <v>0.2323387278952609</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1727803361695166</v>
+        <v>0.1827652992560189</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.1394737357079521</v>
+        <v>-0.1339178226704476</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1030395225153029</v>
+        <v>-0.09755297071083646</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2310575188644108</v>
+        <v>0.2167169468923618</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.1419956628939829</v>
+        <v>0.127729300746239</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.02056268051775589</v>
+        <v>-0.01507247430370029</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.2796645690254778</v>
+        <v>0.2848181771280878</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.2336159415805454</v>
+        <v>0.2388036615968048</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.3147016125182702</v>
+        <v>0.3198032394167143</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.04089179463143466</v>
+        <v>-0.03520185366723183</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1399228844264897</v>
+        <v>-0.1542399137872863</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.1312420509075949</v>
+        <v>-0.1457443203572097</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.01317776214347788</v>
+        <v>-0.007477772964499252</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.1116489714143256</v>
+        <v>0.1171894343538114</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.1634518676372423</v>
+        <v>0.1689293856896654</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.3659718701473409</v>
+        <v>0.371150369406557</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.006680366403145399</v>
+        <v>-0.00101414312064918</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1200733749587712</v>
+        <v>-0.1345623560764651</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.1073209028772766</v>
+        <v>-0.1218594932675288</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.0650704630428578</v>
+        <v>0.07069238505890496</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.02463174049077566</v>
+        <v>-0.01888250636923061</v>
       </c>
     </row>
     <row r="10">
@@ -1578,79 +1578,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2927</v>
+        <v>2931</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1750470309459544</v>
+        <v>0.1714199146940913</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.01438268963399025</v>
+        <v>0.02437608821821868</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.2224898329845644</v>
+        <v>0.2323387278952609</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1727803361695166</v>
+        <v>0.1827652992560189</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1394737357079521</v>
+        <v>-0.1339178226704476</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1030395225153029</v>
+        <v>-0.09755297071083646</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2310575188644108</v>
+        <v>0.2167169468923618</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.1419956628939829</v>
+        <v>0.127729300746239</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.02056268051775589</v>
+        <v>-0.01507247430370029</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2796645690254778</v>
+        <v>0.2848181771280878</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2336159415805454</v>
+        <v>0.2388036615968048</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3147016125182702</v>
+        <v>0.3198032394167143</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.04089179463143466</v>
+        <v>-0.03520185366723183</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1399228844264897</v>
+        <v>-0.1542399137872863</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.1312420509075949</v>
+        <v>-0.1457443203572097</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.01317776214347788</v>
+        <v>-0.007477772964499252</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.1116489714143256</v>
+        <v>0.1171894343538114</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.1634518676372423</v>
+        <v>0.1689293856896654</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.3659718701473409</v>
+        <v>0.371150369406557</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.006680366403145399</v>
+        <v>-0.00101414312064918</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.1200733749587712</v>
+        <v>-0.1345623560764651</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.1073209028772766</v>
+        <v>-0.1218594932675288</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.0650704630428578</v>
+        <v>0.07069238505890496</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.02463174049077566</v>
+        <v>-0.01888250636923061</v>
       </c>
     </row>
     <row r="11">
@@ -1660,79 +1660,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2435</v>
+        <v>2438</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3354890069653393</v>
+        <v>-0.361824710173309</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.251022926428611</v>
+        <v>-0.2673924529390774</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4124347413384015</v>
+        <v>0.3955702475035707</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.2520745689530841</v>
+        <v>0.2355563639532932</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2128032713958206</v>
+        <v>-0.1996375548019671</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1251673684021455</v>
+        <v>-0.1350703895124283</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.2694523000655877</v>
+        <v>0.235371787470342</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.05007135197411117</v>
+        <v>-0.06027527289985812</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.008548062732785411</v>
+        <v>0.004595047488692217</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.672338788029343</v>
+        <v>0.6848201758888592</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4389227793483172</v>
+        <v>0.4516226991563599</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.511075428543748</v>
+        <v>0.5237459747543411</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1802279353299667</v>
+        <v>-0.1905853480298205</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2545462235082141</v>
+        <v>-0.2890150012548176</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.4220729400550809</v>
+        <v>-0.4321820511491623</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.07264527171566471</v>
+        <v>-0.05889500570351203</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.06349707635919088</v>
+        <v>0.07710631903165677</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.1469789880380503</v>
+        <v>0.1605050584642456</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.4287641931106307</v>
+        <v>0.4418896634233818</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.1391657558975865</v>
+        <v>-0.1496340472968427</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.2066460716373086</v>
+        <v>-0.2415452296012575</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.2826284481678698</v>
+        <v>-0.2929622079947904</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.08987987209402348</v>
+        <v>-0.07603930053898722</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.3056239050648912</v>
+        <v>-0.2915050255686822</v>
       </c>
     </row>
     <row r="12">
@@ -1742,79 +1742,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2435</v>
+        <v>2438</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3354890069653393</v>
+        <v>-0.361824710173309</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.251022926428611</v>
+        <v>-0.2673924529390774</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4124347413384015</v>
+        <v>0.3955702475035707</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2520745689530841</v>
+        <v>0.2355563639532932</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2128032713958206</v>
+        <v>-0.1996375548019671</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1251673684021455</v>
+        <v>-0.1350703895124283</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.2694523000655877</v>
+        <v>0.235371787470342</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.05007135197411117</v>
+        <v>-0.06027527289985812</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.008548062732785411</v>
+        <v>0.004595047488692217</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.672338788029343</v>
+        <v>0.6848201758888592</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4389227793483172</v>
+        <v>0.4516226991563599</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.511075428543748</v>
+        <v>0.5237459747543411</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1802279353299667</v>
+        <v>-0.1905853480298205</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2545462235082141</v>
+        <v>-0.2890150012548176</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.4220729400550809</v>
+        <v>-0.4321820511491623</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.07264527171566471</v>
+        <v>-0.05889500570351203</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.06349707635919088</v>
+        <v>0.07710631903165677</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.1469789880380503</v>
+        <v>0.1605050584642456</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.4287641931106307</v>
+        <v>0.4418896634233818</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.1391657558975865</v>
+        <v>-0.1496340472968427</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.2066460716373086</v>
+        <v>-0.2415452296012575</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.2826284481678698</v>
+        <v>-0.2929622079947904</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.08987987209402348</v>
+        <v>-0.07603930053898722</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.3056239050648912</v>
+        <v>-0.2915050255686822</v>
       </c>
     </row>
     <row r="13">
@@ -1824,79 +1824,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2435</v>
+        <v>2438</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3354890069653393</v>
+        <v>-0.361824710173309</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.251022926428611</v>
+        <v>-0.2673924529390774</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4124347413384015</v>
+        <v>0.3955702475035707</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.2520745689530841</v>
+        <v>0.2355563639532932</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2128032713958206</v>
+        <v>-0.1996375548019671</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1251673684021455</v>
+        <v>-0.1350703895124283</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2694523000655877</v>
+        <v>0.235371787470342</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.05007135197411117</v>
+        <v>-0.06027527289985812</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.008548062732785411</v>
+        <v>0.004595047488692217</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.672338788029343</v>
+        <v>0.6848201758888592</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.4389227793483172</v>
+        <v>0.4516226991563599</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.511075428543748</v>
+        <v>0.5237459747543411</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1802279353299667</v>
+        <v>-0.1905853480298205</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2545462235082141</v>
+        <v>-0.2890150012548176</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.4220729400550809</v>
+        <v>-0.4321820511491623</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.07264527171566471</v>
+        <v>-0.05889500570351203</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.06349707635919088</v>
+        <v>0.07710631903165677</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.1469789880380503</v>
+        <v>0.1605050584642456</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.4287641931106307</v>
+        <v>0.4418896634233818</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.1391657558975865</v>
+        <v>-0.1496340472968427</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2066460716373086</v>
+        <v>-0.2415452296012575</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.2826284481678698</v>
+        <v>-0.2929622079947904</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.08987987209402348</v>
+        <v>-0.07603930053898722</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.3056239050648912</v>
+        <v>-0.2915050255686822</v>
       </c>
     </row>
     <row r="14">
@@ -1906,79 +1906,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2435</v>
+        <v>2438</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.3354890069653393</v>
+        <v>-0.361824710173309</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.251022926428611</v>
+        <v>-0.2673924529390774</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4124347413384015</v>
+        <v>0.3955702475035707</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.2520745689530841</v>
+        <v>0.2355563639532932</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2128032713958206</v>
+        <v>-0.1996375548019671</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1251673684021455</v>
+        <v>-0.1350703895124283</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.2694523000655877</v>
+        <v>0.235371787470342</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.05007135197411117</v>
+        <v>-0.06027527289985812</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.008548062732785411</v>
+        <v>0.004595047488692217</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.672338788029343</v>
+        <v>0.6848201758888592</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4389227793483172</v>
+        <v>0.4516226991563599</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.511075428543748</v>
+        <v>0.5237459747543411</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.1802279353299667</v>
+        <v>-0.1905853480298205</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2545462235082141</v>
+        <v>-0.2890150012548176</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.4220729400550809</v>
+        <v>-0.4321820511491623</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.07264527171566471</v>
+        <v>-0.05889500570351203</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.06349707635919088</v>
+        <v>0.07710631903165677</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.1469789880380503</v>
+        <v>0.1605050584642456</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.4287641931106307</v>
+        <v>0.4418896634233818</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.1391657558975865</v>
+        <v>-0.1496340472968427</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.2066460716373086</v>
+        <v>-0.2415452296012575</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.2826284481678698</v>
+        <v>-0.2929622079947904</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.08987987209402348</v>
+        <v>-0.07603930053898722</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.3056239050648912</v>
+        <v>-0.2915050255686822</v>
       </c>
     </row>
     <row r="15">
@@ -1988,79 +1988,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2435</v>
+        <v>2438</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.3354890069653393</v>
+        <v>-0.361824710173309</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.251022926428611</v>
+        <v>-0.2673924529390774</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4124347413384015</v>
+        <v>0.3955702475035707</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2520745689530841</v>
+        <v>0.2355563639532932</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.2128032713958206</v>
+        <v>-0.1996375548019671</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1251673684021455</v>
+        <v>-0.1350703895124283</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2694523000655877</v>
+        <v>0.235371787470342</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.05007135197411117</v>
+        <v>-0.06027527289985812</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.008548062732785411</v>
+        <v>0.004595047488692217</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.672338788029343</v>
+        <v>0.6848201758888592</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.4389227793483172</v>
+        <v>0.4516226991563599</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.511075428543748</v>
+        <v>0.5237459747543411</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.1802279353299667</v>
+        <v>-0.1905853480298205</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.2545462235082141</v>
+        <v>-0.2890150012548176</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.4220729400550809</v>
+        <v>-0.4321820511491623</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.07264527171566471</v>
+        <v>-0.05889500570351203</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.06349707635919088</v>
+        <v>0.07710631903165677</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.1469789880380503</v>
+        <v>0.1605050584642456</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.4287641931106307</v>
+        <v>0.4418896634233818</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.1391657558975865</v>
+        <v>-0.1496340472968427</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.2066460716373086</v>
+        <v>-0.2415452296012575</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.2826284481678698</v>
+        <v>-0.2929622079947904</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.08987987209402348</v>
+        <v>-0.07603930053898722</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.3056239050648912</v>
+        <v>-0.2915050255686822</v>
       </c>
     </row>
     <row r="16">
@@ -2070,79 +2070,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.4909282542489137</v>
+        <v>-0.552536751002151</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.0138620710558186</v>
+        <v>0.008032880863773073</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2893594242550463</v>
+        <v>0.2838532067907025</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.934491263587077</v>
+        <v>0.9286177436708698</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.06728807607038334</v>
+        <v>-0.07179440576802421</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.1488592081351996</v>
+        <v>0.115171780329355</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.1954355044943696</v>
+        <v>0.1612190064594614</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.08320507313813152</v>
+        <v>-0.08772973294473729</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.3169247734802454</v>
+        <v>0.3412896146109077</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.110098669962895</v>
+        <v>1.133978333775666</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.5431235431235422</v>
+        <v>0.5674595887568756</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.4478378183163372</v>
+        <v>0.4423987098990523</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3388988332205756</v>
+        <v>-0.3733863077767481</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.5603252365528135</v>
+        <v>-0.5944651842233384</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.398098519499996</v>
+        <v>-0.4023719490464188</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.1457953478506511</v>
+        <v>0.1713286713286664</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.5045707752822892</v>
+        <v>0.5297876378099104</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.1735470851681455</v>
+        <v>0.1991427254386622</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.6776301564039144</v>
+        <v>0.6717076176566295</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.1241150099364248</v>
+        <v>0.0885328937437535</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.04371375726658044</v>
+        <v>0.007999046106263563</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.1220523683903423</v>
+        <v>0.1169791056697704</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.1175005414771491</v>
+        <v>-0.09156720504722671</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.04308218566675492</v>
+        <v>0.06887718328808745</v>
       </c>
     </row>
     <row r="17">
@@ -2152,79 +2152,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4909282542489137</v>
+        <v>-0.552536751002151</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.0138620710558186</v>
+        <v>0.008032880863773073</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2893594242550463</v>
+        <v>0.2838532067907025</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.934491263587077</v>
+        <v>0.9286177436708698</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.06728807607038334</v>
+        <v>-0.07179440576802421</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1488592081351996</v>
+        <v>0.115171780329355</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.1954355044943696</v>
+        <v>0.1612190064594614</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.08320507313813152</v>
+        <v>-0.08772973294473729</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.3169247734802454</v>
+        <v>0.3412896146109077</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.110098669962895</v>
+        <v>1.133978333775666</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.5431235431235422</v>
+        <v>0.5674595887568756</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.4478378183163372</v>
+        <v>0.4423987098990523</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.3388988332205756</v>
+        <v>-0.3733863077767481</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.5603252365528135</v>
+        <v>-0.5944651842233384</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.398098519499996</v>
+        <v>-0.4023719490464188</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.1457953478506511</v>
+        <v>0.1713286713286664</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.5045707752822892</v>
+        <v>0.5297876378099104</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.1735470851681455</v>
+        <v>0.1991427254386622</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.6776301564039144</v>
+        <v>0.6717076176566295</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.1241150099364248</v>
+        <v>0.0885328937437535</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.04371375726658044</v>
+        <v>0.007999046106263563</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.1220523683903423</v>
+        <v>0.1169791056697704</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.1175005414771491</v>
+        <v>-0.09156720504722671</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.04308218566675492</v>
+        <v>0.06887718328808745</v>
       </c>
     </row>
     <row r="18">
@@ -2234,79 +2234,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.4909282542489137</v>
+        <v>-0.552536751002151</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.0138620710558186</v>
+        <v>0.008032880863773073</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.2893594242550463</v>
+        <v>0.2838532067907025</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.934491263587077</v>
+        <v>0.9286177436708698</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.06728807607038334</v>
+        <v>-0.07179440576802421</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1488592081351996</v>
+        <v>0.115171780329355</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.1954355044943696</v>
+        <v>0.1612190064594614</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.08320507313813152</v>
+        <v>-0.08772973294473729</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.3169247734802454</v>
+        <v>0.3412896146109077</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.110098669962895</v>
+        <v>1.133978333775666</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.5431235431235422</v>
+        <v>0.5674595887568756</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.4478378183163372</v>
+        <v>0.4423987098990523</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.3388988332205756</v>
+        <v>-0.3733863077767481</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.5603252365528135</v>
+        <v>-0.5944651842233384</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.398098519499996</v>
+        <v>-0.4023719490464188</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.1457953478506511</v>
+        <v>0.1713286713286664</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.5045707752822892</v>
+        <v>0.5297876378099104</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.1735470851681455</v>
+        <v>0.1991427254386622</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.6776301564039144</v>
+        <v>0.6717076176566295</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.1241150099364248</v>
+        <v>0.0885328937437535</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.04371375726658044</v>
+        <v>0.007999046106263563</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.1220523683903423</v>
+        <v>0.1169791056697704</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.1175005414771491</v>
+        <v>-0.09156720504722671</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.04308218566675492</v>
+        <v>0.06887718328808745</v>
       </c>
     </row>
     <row r="19">
@@ -2316,79 +2316,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.4909282542489137</v>
+        <v>-0.552536751002151</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.0138620710558186</v>
+        <v>0.008032880863773073</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2893594242550463</v>
+        <v>0.2838532067907025</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.934491263587077</v>
+        <v>0.9286177436708698</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.06728807607038334</v>
+        <v>-0.07179440576802421</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.1488592081351996</v>
+        <v>0.115171780329355</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.1954355044943696</v>
+        <v>0.1612190064594614</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.08320507313813152</v>
+        <v>-0.08772973294473729</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.3169247734802454</v>
+        <v>0.3412896146109077</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.110098669962895</v>
+        <v>1.133978333775666</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.5431235431235422</v>
+        <v>0.5674595887568756</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.4478378183163372</v>
+        <v>0.4423987098990523</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.3388988332205756</v>
+        <v>-0.3733863077767481</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.5603252365528135</v>
+        <v>-0.5944651842233384</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.398098519499996</v>
+        <v>-0.4023719490464188</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.1457953478506511</v>
+        <v>0.1713286713286664</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.5045707752822892</v>
+        <v>0.5297876378099104</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.1735470851681455</v>
+        <v>0.1991427254386622</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.6776301564039144</v>
+        <v>0.6717076176566295</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.1241150099364248</v>
+        <v>0.0885328937437535</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.04371375726658044</v>
+        <v>0.007999046106263563</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.1220523683903423</v>
+        <v>0.1169791056697704</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.1175005414771491</v>
+        <v>-0.09156720504722671</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.04308218566675492</v>
+        <v>0.06887718328808745</v>
       </c>
     </row>
     <row r="20">
@@ -2398,79 +2398,79 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.4909282542489137</v>
+        <v>-0.552536751002151</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.0138620710558186</v>
+        <v>0.008032880863773073</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.2893594242550463</v>
+        <v>0.2838532067907025</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.934491263587077</v>
+        <v>0.9286177436708698</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.06728807607038334</v>
+        <v>-0.07179440576802421</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.1488592081351996</v>
+        <v>0.115171780329355</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.1954355044943696</v>
+        <v>0.1612190064594614</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.08320507313813152</v>
+        <v>-0.08772973294473729</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.3169247734802454</v>
+        <v>0.3412896146109077</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.110098669962895</v>
+        <v>1.133978333775666</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.5431235431235422</v>
+        <v>0.5674595887568756</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.4478378183163372</v>
+        <v>0.4423987098990523</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.3388988332205756</v>
+        <v>-0.3733863077767481</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.5603252365528135</v>
+        <v>-0.5944651842233384</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.398098519499996</v>
+        <v>-0.4023719490464188</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.1457953478506511</v>
+        <v>0.1713286713286664</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.5045707752822892</v>
+        <v>0.5297876378099104</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.1735470851681455</v>
+        <v>0.1991427254386622</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.6776301564039144</v>
+        <v>0.6717076176566295</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.1241150099364248</v>
+        <v>0.0885328937437535</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.04371375726658044</v>
+        <v>0.007999046106263563</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.1220523683903423</v>
+        <v>0.1169791056697704</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.1175005414771491</v>
+        <v>-0.09156720504722671</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.04308218566675492</v>
+        <v>0.06887718328808745</v>
       </c>
     </row>
     <row r="21">
@@ -2480,79 +2480,79 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8999262092591351</v>
+        <v>-0.9519430970943219</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.1672363041846623</v>
+        <v>0.1796894397168529</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.8104635299343244</v>
+        <v>0.8235758530931605</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.431799663962948</v>
+        <v>1.405782024516128</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.05543157954968336</v>
+        <v>-0.08883598722677277</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.3367007381898404</v>
+        <v>0.3026291763757101</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.04174697990419673</v>
+        <v>0.007844773330624832</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.3778605006323588</v>
+        <v>0.3824677178844524</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.760913844518484</v>
+        <v>0.8046429879310608</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.188576398228847</v>
+        <v>1.232607596868178</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.5459998278055735</v>
+        <v>0.5503830860246381</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.3752475466770093</v>
+        <v>0.3399396935055989</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.3388988332205756</v>
+        <v>-0.3733863077767481</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.5603252365528135</v>
+        <v>-0.5944651842233384</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.1243134407867927</v>
+        <v>-0.1187660515852826</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.2655763197876837</v>
+        <v>0.3114247813290234</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.3778918663883815</v>
+        <v>0.4237644011968769</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.1769635236613354</v>
+        <v>0.1820311580190932</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.9829750137815196</v>
+        <v>0.9454926963698327</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.6213715257114458</v>
+        <v>0.5847683489114459</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.2151815213269472</v>
+        <v>0.1791147203020174</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.06656217207604698</v>
+        <v>-0.0610960503482616</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.07111399898924731</v>
+        <v>0.1173286372527897</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.1048282208330278</v>
+        <v>0.1510759201569201</v>
       </c>
     </row>
     <row r="22">
@@ -2562,79 +2562,79 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.8999262092591351</v>
+        <v>-0.9519430970943219</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.1672363041846623</v>
+        <v>0.1796894397168529</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.8104635299343244</v>
+        <v>0.8235758530931605</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.431799663962948</v>
+        <v>1.405782024516128</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.05543157954968336</v>
+        <v>-0.08883598722677277</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.3367007381898404</v>
+        <v>0.3026291763757101</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.04174697990419673</v>
+        <v>0.007844773330624832</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.3778605006323588</v>
+        <v>0.3824677178844524</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.760913844518484</v>
+        <v>0.8046429879310608</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.188576398228847</v>
+        <v>1.232607596868178</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.5459998278055735</v>
+        <v>0.5503830860246381</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.3752475466770093</v>
+        <v>0.3399396935055989</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.3388988332205756</v>
+        <v>-0.3733863077767481</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.5603252365528135</v>
+        <v>-0.5944651842233384</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.1243134407867927</v>
+        <v>-0.1187660515852826</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.2655763197876837</v>
+        <v>0.3114247813290234</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.3778918663883815</v>
+        <v>0.4237644011968769</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.1769635236613354</v>
+        <v>0.1820311580190932</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.9829750137815196</v>
+        <v>0.9454926963698327</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.6213715257114458</v>
+        <v>0.5847683489114459</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.2151815213269472</v>
+        <v>0.1791147203020174</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.06656217207604698</v>
+        <v>-0.0610960503482616</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.07111399898924731</v>
+        <v>0.1173286372527897</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.1048282208330278</v>
+        <v>0.1510759201569201</v>
       </c>
     </row>
     <row r="23">
@@ -2644,79 +2644,79 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.8999262092591351</v>
+        <v>-0.9519430970943219</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1672363041846623</v>
+        <v>0.1796894397168529</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.8104635299343244</v>
+        <v>0.8235758530931605</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.431799663962948</v>
+        <v>1.405782024516128</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.05543157954968336</v>
+        <v>-0.08883598722677277</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.3367007381898404</v>
+        <v>0.3026291763757101</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.04174697990419673</v>
+        <v>0.007844773330624832</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.3778605006323588</v>
+        <v>0.3824677178844524</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.760913844518484</v>
+        <v>0.8046429879310608</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.188576398228847</v>
+        <v>1.232607596868178</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.5459998278055735</v>
+        <v>0.5503830860246381</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.3752475466770093</v>
+        <v>0.3399396935055989</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.3388988332205756</v>
+        <v>-0.3733863077767481</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.5603252365528135</v>
+        <v>-0.5944651842233384</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.1243134407867927</v>
+        <v>-0.1187660515852826</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.2655763197876837</v>
+        <v>0.3114247813290234</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.3778918663883815</v>
+        <v>0.4237644011968769</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.1769635236613354</v>
+        <v>0.1820311580190932</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.9829750137815196</v>
+        <v>0.9454926963698327</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.6213715257114458</v>
+        <v>0.5847683489114459</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.2151815213269472</v>
+        <v>0.1791147203020174</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.06656217207604698</v>
+        <v>-0.0610960503482616</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.07111399898924731</v>
+        <v>0.1173286372527897</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.1048282208330278</v>
+        <v>0.1510759201569201</v>
       </c>
     </row>
     <row r="24">
@@ -2726,79 +2726,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.8999262092591351</v>
+        <v>-0.9519430970943219</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.1672363041846623</v>
+        <v>0.1796894397168529</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.8104635299343244</v>
+        <v>0.8235758530931605</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.431799663962948</v>
+        <v>1.405782024516128</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05543157954968336</v>
+        <v>-0.08883598722677277</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.3367007381898404</v>
+        <v>0.3026291763757101</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.04174697990419673</v>
+        <v>0.007844773330624832</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.3778605006323588</v>
+        <v>0.3824677178844524</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.760913844518484</v>
+        <v>0.8046429879310608</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.188576398228847</v>
+        <v>1.232607596868178</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.5459998278055735</v>
+        <v>0.5503830860246381</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.3752475466770093</v>
+        <v>0.3399396935055989</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.3388988332205756</v>
+        <v>-0.3733863077767481</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.5603252365528135</v>
+        <v>-0.5944651842233384</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.1243134407867927</v>
+        <v>-0.1187660515852826</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.2655763197876837</v>
+        <v>0.3114247813290234</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.3778918663883815</v>
+        <v>0.4237644011968769</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.1769635236613354</v>
+        <v>0.1820311580190932</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.9829750137815196</v>
+        <v>0.9454926963698327</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.6213715257114458</v>
+        <v>0.5847683489114459</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.2151815213269472</v>
+        <v>0.1791147203020174</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.06656217207604698</v>
+        <v>-0.0610960503482616</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.07111399898924731</v>
+        <v>0.1173286372527897</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.1048282208330278</v>
+        <v>0.1510759201569201</v>
       </c>
     </row>
     <row r="25">
@@ -2808,79 +2808,79 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.8999262092591351</v>
+        <v>-0.9519430970943219</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.1672363041846623</v>
+        <v>0.1796894397168529</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.8104635299343244</v>
+        <v>0.8235758530931605</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.431799663962948</v>
+        <v>1.405782024516128</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.05543157954968336</v>
+        <v>-0.08883598722677277</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.3367007381898404</v>
+        <v>0.3026291763757101</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.04174697990419673</v>
+        <v>0.007844773330624832</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.3778605006323588</v>
+        <v>0.3824677178844524</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.760913844518484</v>
+        <v>0.8046429879310608</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.188576398228847</v>
+        <v>1.232607596868178</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.5459998278055735</v>
+        <v>0.5503830860246381</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.3752475466770093</v>
+        <v>0.3399396935055989</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.3388988332205756</v>
+        <v>-0.3733863077767481</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.5603252365528135</v>
+        <v>-0.5944651842233384</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.1243134407867927</v>
+        <v>-0.1187660515852826</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.2655763197876837</v>
+        <v>0.3114247813290234</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.3778918663883815</v>
+        <v>0.4237644011968769</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.1769635236613354</v>
+        <v>0.1820311580190932</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.9829750137815196</v>
+        <v>0.9454926963698327</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.6213715257114458</v>
+        <v>0.5847683489114459</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.2151815213269472</v>
+        <v>0.1791147203020174</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.06656217207604698</v>
+        <v>-0.0610960503482616</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.07111399898924731</v>
+        <v>0.1173286372527897</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>0.1048282208330278</v>
+        <v>0.1510759201569201</v>
       </c>
     </row>
     <row r="26">
@@ -2890,79 +2890,79 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.9405645882868754</v>
+        <v>0.9046074320225728</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.08748170295766</v>
+        <v>1.136850525846029</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.239080240889294</v>
+        <v>1.232573808103382</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.017599473731877</v>
+        <v>1.95111263119643</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1920436014076117</v>
+        <v>-0.2251686388968537</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.2000887163319121</v>
+        <v>0.1662965247056292</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.9638781274451844</v>
+        <v>0.9280901721036301</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.1975326317799</v>
+        <v>1.220989740782173</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.6243018226605628</v>
+        <v>0.7077090652543916</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.9353559344820752</v>
+        <v>0.9593835531523283</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.5517583032983424</v>
+        <v>0.516230080560149</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.7859251647468355</v>
+        <v>0.7497757590793697</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.4415682377380321</v>
+        <v>-0.4758453241701872</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.1496476184830087</v>
+        <v>-0.1846291186495677</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.628595525674541</v>
+        <v>0.6538648263087623</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.7104770726966478</v>
+        <v>0.7972434820484082</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.6382784690436338</v>
+        <v>0.663326345070935</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>0.3895647472289738</v>
+        <v>0.353146832214847</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1.223029883466026</v>
+        <v>1.185054640243898</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.8957199482080185</v>
+        <v>0.8585534276246563</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.4552363910114465</v>
+        <v>0.4186766641760755</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>0.3792540144808854</v>
+        <v>0.4047700043617795</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>0.34546242148582</v>
+        <v>0.4326694902526285</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.2865491773872861</v>
+        <v>-0.2604467135879389</v>
       </c>
     </row>
     <row r="27">
@@ -2972,79 +2972,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.9405645882868754</v>
+        <v>0.9046074320225728</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.08748170295766</v>
+        <v>1.136850525846029</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.239080240889294</v>
+        <v>1.232573808103382</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.017599473731877</v>
+        <v>1.95111263119643</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.1920436014076117</v>
+        <v>-0.2251686388968537</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.2000887163319121</v>
+        <v>0.1662965247056292</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.9638781274451844</v>
+        <v>0.9280901721036301</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.1975326317799</v>
+        <v>1.220989740782173</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.6243018226605628</v>
+        <v>0.7077090652543916</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.9353559344820752</v>
+        <v>0.9593835531523283</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.5517583032983424</v>
+        <v>0.516230080560149</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.7859251647468355</v>
+        <v>0.7497757590793697</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.4415682377380321</v>
+        <v>-0.4758453241701872</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.1496476184830087</v>
+        <v>-0.1846291186495677</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.628595525674541</v>
+        <v>0.6538648263087623</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.7104770726966478</v>
+        <v>0.7972434820484082</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.6382784690436338</v>
+        <v>0.663326345070935</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>0.3895647472289738</v>
+        <v>0.353146832214847</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1.223029883466026</v>
+        <v>1.185054640243898</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.8957199482080185</v>
+        <v>0.8585534276246563</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.4552363910114465</v>
+        <v>0.4186766641760755</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>0.3792540144808854</v>
+        <v>0.4047700043617795</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>0.34546242148582</v>
+        <v>0.4326694902526285</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.2865491773872861</v>
+        <v>-0.2604467135879389</v>
       </c>
     </row>
     <row r="28">
@@ -3054,79 +3054,79 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.9405645882868754</v>
+        <v>0.9046074320225728</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.08748170295766</v>
+        <v>1.136850525846029</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.239080240889294</v>
+        <v>1.232573808103382</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.017599473731877</v>
+        <v>1.95111263119643</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1920436014076117</v>
+        <v>-0.2251686388968537</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.2000887163319121</v>
+        <v>0.1662965247056292</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.9638781274451844</v>
+        <v>0.9280901721036301</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.1975326317799</v>
+        <v>1.220989740782173</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.6243018226605628</v>
+        <v>0.7077090652543916</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.9353559344820752</v>
+        <v>0.9593835531523283</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.5517583032983424</v>
+        <v>0.516230080560149</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.7859251647468355</v>
+        <v>0.7497757590793697</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.4415682377380321</v>
+        <v>-0.4758453241701872</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.1496476184830087</v>
+        <v>-0.1846291186495677</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.628595525674541</v>
+        <v>0.6538648263087623</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.7104770726966478</v>
+        <v>0.7972434820484082</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.6382784690436338</v>
+        <v>0.663326345070935</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>0.3895647472289738</v>
+        <v>0.353146832214847</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>1.223029883466026</v>
+        <v>1.185054640243898</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.8957199482080185</v>
+        <v>0.8585534276246563</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.4552363910114465</v>
+        <v>0.4186766641760755</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>0.3792540144808854</v>
+        <v>0.4047700043617795</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.34546242148582</v>
+        <v>0.4326694902526285</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.2865491773872861</v>
+        <v>-0.2604467135879389</v>
       </c>
     </row>
     <row r="29">
@@ -3136,79 +3136,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.9405645882868754</v>
+        <v>0.9046074320225728</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.08748170295766</v>
+        <v>1.136850525846029</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.239080240889294</v>
+        <v>1.232573808103382</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.017599473731877</v>
+        <v>1.95111263119643</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.1920436014076117</v>
+        <v>-0.2251686388968537</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.2000887163319121</v>
+        <v>0.1662965247056292</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.9638781274451844</v>
+        <v>0.9280901721036301</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.1975326317799</v>
+        <v>1.220989740782173</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.6243018226605628</v>
+        <v>0.7077090652543916</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.9353559344820752</v>
+        <v>0.9593835531523283</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.5517583032983424</v>
+        <v>0.516230080560149</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.7859251647468355</v>
+        <v>0.7497757590793697</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.4415682377380321</v>
+        <v>-0.4758453241701872</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.1496476184830087</v>
+        <v>-0.1846291186495677</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.628595525674541</v>
+        <v>0.6538648263087623</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.7104770726966478</v>
+        <v>0.7972434820484082</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.6382784690436338</v>
+        <v>0.663326345070935</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.3895647472289738</v>
+        <v>0.353146832214847</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1.223029883466026</v>
+        <v>1.185054640243898</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.8957199482080185</v>
+        <v>0.8585534276246563</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.4552363910114465</v>
+        <v>0.4186766641760755</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>0.3792540144808854</v>
+        <v>0.4047700043617795</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.34546242148582</v>
+        <v>0.4326694902526285</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.2865491773872861</v>
+        <v>-0.2604467135879389</v>
       </c>
     </row>
     <row r="30">
@@ -3218,79 +3218,79 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.9405645882868754</v>
+        <v>0.9046074320225728</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.08748170295766</v>
+        <v>1.136850525846029</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.239080240889294</v>
+        <v>1.232573808103382</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.017599473731877</v>
+        <v>1.95111263119643</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1920436014076117</v>
+        <v>-0.2251686388968537</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2000887163319121</v>
+        <v>0.1662965247056292</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.9638781274451844</v>
+        <v>0.9280901721036301</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.1975326317799</v>
+        <v>1.220989740782173</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.6243018226605628</v>
+        <v>0.7077090652543916</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.9353559344820752</v>
+        <v>0.9593835531523283</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.5517583032983424</v>
+        <v>0.516230080560149</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.7859251647468355</v>
+        <v>0.7497757590793697</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.4415682377380321</v>
+        <v>-0.4758453241701872</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.1496476184830087</v>
+        <v>-0.1846291186495677</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.628595525674541</v>
+        <v>0.6538648263087623</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.7104770726966478</v>
+        <v>0.7972434820484082</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.6382784690436338</v>
+        <v>0.663326345070935</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.3895647472289738</v>
+        <v>0.353146832214847</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.223029883466026</v>
+        <v>1.185054640243898</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.8957199482080185</v>
+        <v>0.8585534276246563</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.4552363910114465</v>
+        <v>0.4186766641760755</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>0.3792540144808854</v>
+        <v>0.4047700043617795</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>0.34546242148582</v>
+        <v>0.4326694902526285</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.2865491773872861</v>
+        <v>-0.2604467135879389</v>
       </c>
     </row>
     <row r="31">
@@ -3300,79 +3300,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.145063565791993</v>
+        <v>1.164878857938177</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.7807332366999944</v>
+        <v>0.8301020595883628</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.502096835684334</v>
+        <v>1.437072785608493</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.017599473731877</v>
+        <v>1.95111263119643</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1920436014076117</v>
+        <v>-0.2251686388968537</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.6099247819056899</v>
+        <v>0.5752944797158577</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.500763373346828</v>
+        <v>2.461832503391975</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.1975326317799</v>
+        <v>1.280975981700351</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4002883412738569</v>
+        <v>-0.3168810986800281</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.7906710505774797</v>
+        <v>0.7544655203654429</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.6544277078157918</v>
+        <v>0.6186890969535952</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1699087376421033</v>
+        <v>0.1350216607187136</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.3388988332205756</v>
+        <v>-0.3733863077767481</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.2610299995868175</v>
+        <v>0.2252069469242102</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>0.833934334709447</v>
+        <v>0.9215423917275984</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.8131464772140973</v>
+        <v>0.8999128865658577</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.8032258761972813</v>
+        <v>0.7659957495883845</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.6982067225376198</v>
+        <v>0.6611550457672024</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>1.737433175647091</v>
+        <v>1.698401662831159</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>0.8957199482080185</v>
+        <v>0.8585534276246563</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>1.175401000064944</v>
+        <v>1.137362495798257</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>0.2763733560446653</v>
+        <v>0.3639560946429938</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.4775828460039051</v>
+        <v>-0.3903757772370966</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.2251818974017255</v>
+        <v>-0.2604467135879389</v>
       </c>
     </row>
     <row r="32">
@@ -3382,79 +3382,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.145063565791993</v>
+        <v>1.164878857938177</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.7807332366999944</v>
+        <v>0.8301020595883628</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.502096835684334</v>
+        <v>1.437072785608493</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.017599473731877</v>
+        <v>1.95111263119643</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.1920436014076117</v>
+        <v>-0.2251686388968537</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.6099247819056899</v>
+        <v>0.5752944797158577</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.500763373346828</v>
+        <v>2.461832503391975</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.1975326317799</v>
+        <v>1.280975981700351</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.4002883412738569</v>
+        <v>-0.3168810986800281</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.7906710505774797</v>
+        <v>0.7544655203654429</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.6544277078157918</v>
+        <v>0.6186890969535952</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1699087376421033</v>
+        <v>0.1350216607187136</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.3388988332205756</v>
+        <v>-0.3733863077767481</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.2610299995868175</v>
+        <v>0.2252069469242102</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0.833934334709447</v>
+        <v>0.9215423917275984</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0.8131464772140973</v>
+        <v>0.8999128865658577</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.8032258761972813</v>
+        <v>0.7659957495883845</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.6982067225376198</v>
+        <v>0.6611550457672024</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>1.737433175647091</v>
+        <v>1.698401662831159</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.8957199482080185</v>
+        <v>0.8585534276246563</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>1.175401000064944</v>
+        <v>1.137362495798257</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>0.2763733560446653</v>
+        <v>0.3639560946429938</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.4775828460039051</v>
+        <v>-0.3903757772370966</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.2251818974017255</v>
+        <v>-0.2604467135879389</v>
       </c>
     </row>
     <row r="33">
@@ -3464,79 +3464,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.145063565791993</v>
+        <v>1.164878857938177</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.7807332366999944</v>
+        <v>0.8301020595883628</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.502096835684334</v>
+        <v>1.437072785608493</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2.017599473731877</v>
+        <v>1.95111263119643</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.1920436014076117</v>
+        <v>-0.2251686388968537</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.6099247819056899</v>
+        <v>0.5752944797158577</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.500763373346828</v>
+        <v>2.461832503391975</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.1975326317799</v>
+        <v>1.280975981700351</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4002883412738569</v>
+        <v>-0.3168810986800281</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.7906710505774797</v>
+        <v>0.7544655203654429</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.6544277078157918</v>
+        <v>0.6186890969535952</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.1699087376421033</v>
+        <v>0.1350216607187136</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.3388988332205756</v>
+        <v>-0.3733863077767481</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.2610299995868175</v>
+        <v>0.2252069469242102</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>0.833934334709447</v>
+        <v>0.9215423917275984</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>0.8131464772140973</v>
+        <v>0.8999128865658577</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.8032258761972813</v>
+        <v>0.7659957495883845</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>0.6982067225376198</v>
+        <v>0.6611550457672024</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>1.737433175647091</v>
+        <v>1.698401662831159</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>0.8957199482080185</v>
+        <v>0.8585534276246563</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>1.175401000064944</v>
+        <v>1.137362495798257</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>0.2763733560446653</v>
+        <v>0.3639560946429938</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.4775828460039051</v>
+        <v>-0.3903757772370966</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.2251818974017255</v>
+        <v>-0.2604467135879389</v>
       </c>
     </row>
     <row r="34">
@@ -3546,79 +3546,79 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.145063565791993</v>
+        <v>1.164878857938177</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.7807332366999944</v>
+        <v>0.8301020595883628</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.502096835684334</v>
+        <v>1.437072785608493</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2.017599473731877</v>
+        <v>1.95111263119643</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1920436014076117</v>
+        <v>-0.2251686388968537</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.6099247819056899</v>
+        <v>0.5752944797158577</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.500763373346828</v>
+        <v>2.461832503391975</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.1975326317799</v>
+        <v>1.280975981700351</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.4002883412738569</v>
+        <v>-0.3168810986800281</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.7906710505774797</v>
+        <v>0.7544655203654429</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.6544277078157918</v>
+        <v>0.6186890969535952</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1699087376421033</v>
+        <v>0.1350216607187136</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3388988332205756</v>
+        <v>-0.3733863077767481</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.2610299995868175</v>
+        <v>0.2252069469242102</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>0.833934334709447</v>
+        <v>0.9215423917275984</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0.8131464772140973</v>
+        <v>0.8999128865658577</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>0.8032258761972813</v>
+        <v>0.7659957495883845</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>0.6982067225376198</v>
+        <v>0.6611550457672024</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>1.737433175647091</v>
+        <v>1.698401662831159</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>0.8957199482080185</v>
+        <v>0.8585534276246563</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>1.175401000064944</v>
+        <v>1.137362495798257</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>0.2763733560446653</v>
+        <v>0.3639560946429938</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.4775828460039051</v>
+        <v>-0.3903757772370966</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.2251818974017255</v>
+        <v>-0.2604467135879389</v>
       </c>
     </row>
     <row r="35">
@@ -3880,79 +3880,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.039694663642663</v>
+        <v>-1.019879371496479</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.08559879527620495</v>
+        <v>-0.1449787504914539</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.323702137655623</v>
+        <v>-1.381384896296645</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.027606686228381</v>
+        <v>-1.086274399610353</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.8292347559363265</v>
+        <v>0.7956770633262522</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.6124086368485564</v>
+        <v>0.5794174429720158</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.372808410061019</v>
+        <v>-1.289794193019993</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.8433681796127246</v>
+        <v>-0.7599248296922738</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1223770864821603</v>
+        <v>0.08964316030324682</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.663834348918741</v>
+        <v>-1.693373525834261</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-1.389400073610602</v>
+        <v>-1.419313883672338</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-1.871009384546952</v>
+        <v>-1.900083489140535</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2430330142467625</v>
+        <v>0.2090776763265865</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.83132321010482</v>
+        <v>0.9179460456167163</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.7794821404107211</v>
+        <v>0.8670901974288725</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.07842505908514141</v>
+        <v>0.04447307078885387</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.664232115939555</v>
+        <v>-0.6967315155813267</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.9720910261914995</v>
+        <v>-1.004001369200076</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-2.175788136717792</v>
+        <v>-2.205114036858745</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.03970278612820266</v>
+        <v>0.006023271084984572</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.7133771100491657</v>
+        <v>0.800823433526034</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0.6373947335186045</v>
+        <v>0.7249774721169331</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.3872486093281964</v>
+        <v>-0.4204261115470516</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.146538830114828</v>
+        <v>0.1122609050065435</v>
       </c>
     </row>
     <row r="8">
@@ -3962,79 +3962,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.039694663642663</v>
+        <v>-1.019879371496479</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.08559879527620495</v>
+        <v>-0.1449787504914539</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.323702137655623</v>
+        <v>-1.381384896296645</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.027606686228381</v>
+        <v>-1.086274399610353</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.8292347559363265</v>
+        <v>0.7956770633262522</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.6124086368485564</v>
+        <v>0.5794174429720158</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.372808410061019</v>
+        <v>-1.289794193019993</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.8433681796127246</v>
+        <v>-0.7599248296922738</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1223770864821603</v>
+        <v>0.08964316030324682</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.663834348918741</v>
+        <v>-1.693373525834261</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.389400073610602</v>
+        <v>-1.419313883672338</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.871009384546952</v>
+        <v>-1.900083489140535</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.2430330142467625</v>
+        <v>0.2090776763265865</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.83132321010482</v>
+        <v>0.9179460456167163</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.7794821404107211</v>
+        <v>0.8670901974288725</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.07842505908514141</v>
+        <v>0.04447307078885387</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.664232115939555</v>
+        <v>-0.6967315155813267</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.9720910261914995</v>
+        <v>-1.004001369200076</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-2.175788136717792</v>
+        <v>-2.205114036858745</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.03970278612820266</v>
+        <v>0.006023271084984572</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.7133771100491657</v>
+        <v>0.800823433526034</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.6373947335186045</v>
+        <v>0.7249774721169331</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.3872486093281964</v>
+        <v>-0.4204261115470516</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.146538830114828</v>
+        <v>0.1122609050065435</v>
       </c>
     </row>
     <row r="9">
@@ -4044,79 +4044,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.039694663642663</v>
+        <v>-1.019879371496479</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.08559879527620495</v>
+        <v>-0.1449787504914539</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.323702137655623</v>
+        <v>-1.381384896296645</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.027606686228381</v>
+        <v>-1.086274399610353</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.8292347559363265</v>
+        <v>0.7956770633262522</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.6124086368485564</v>
+        <v>0.5794174429720158</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.372808410061019</v>
+        <v>-1.289794193019993</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.8433681796127246</v>
+        <v>-0.7599248296922738</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1223770864821603</v>
+        <v>0.08964316030324682</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.663834348918741</v>
+        <v>-1.693373525834261</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.389400073610602</v>
+        <v>-1.419313883672338</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.871009384546952</v>
+        <v>-1.900083489140535</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2430330142467625</v>
+        <v>0.2090776763265865</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.83132321010482</v>
+        <v>0.9179460456167163</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.7794821404107211</v>
+        <v>0.8670901974288725</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.07842505908514141</v>
+        <v>0.04447307078885387</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.664232115939555</v>
+        <v>-0.6967315155813267</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.9720910261914995</v>
+        <v>-1.004001369200076</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-2.175788136717792</v>
+        <v>-2.205114036858745</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.03970278612820266</v>
+        <v>0.006023271084984572</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.7133771100491657</v>
+        <v>0.800823433526034</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.6373947335186045</v>
+        <v>0.7249774721169331</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.3872486093281964</v>
+        <v>-0.4204261115470516</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.146538830114828</v>
+        <v>0.1122609050065435</v>
       </c>
     </row>
     <row r="10">
@@ -4126,79 +4126,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.039694663642663</v>
+        <v>-1.019879371496479</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.08559879527620495</v>
+        <v>-0.1449787504914539</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.323702137655623</v>
+        <v>-1.381384896296645</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.027606686228381</v>
+        <v>-1.086274399610353</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.8292347559363265</v>
+        <v>0.7956770633262522</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.6124086368485564</v>
+        <v>0.5794174429720158</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.372808410061019</v>
+        <v>-1.289794193019993</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.8433681796127246</v>
+        <v>-0.7599248296922738</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1223770864821603</v>
+        <v>0.08964316030324682</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.663834348918741</v>
+        <v>-1.693373525834261</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.389400073610602</v>
+        <v>-1.419313883672338</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.871009384546952</v>
+        <v>-1.900083489140535</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.2430330142467625</v>
+        <v>0.2090776763265865</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.83132321010482</v>
+        <v>0.9179460456167163</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.7794821404107211</v>
+        <v>0.8670901974288725</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.07842505908514141</v>
+        <v>0.04447307078885387</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.664232115939555</v>
+        <v>-0.6967315155813267</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.9720910261914995</v>
+        <v>-1.004001369200076</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-2.175788136717792</v>
+        <v>-2.205114036858745</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.03970278612820266</v>
+        <v>0.006023271084984572</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.7133771100491657</v>
+        <v>0.800823433526034</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.6373947335186045</v>
+        <v>0.7249774721169331</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.3872486093281964</v>
+        <v>-0.4204261115470516</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.146538830114828</v>
+        <v>0.1122609050065435</v>
       </c>
     </row>
     <row r="11">
@@ -4208,79 +4208,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.8297513179334501</v>
+        <v>0.8954432091486808</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.6214719117944938</v>
+        <v>0.6614728624117703</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.020671834625325</v>
+        <v>-0.9781590898450361</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.6235662821879728</v>
+        <v>-0.5822421415458408</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.5262044529060219</v>
+        <v>0.4932577084875405</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.3093783338182519</v>
+        <v>0.3340641016094281</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.6657377029903202</v>
+        <v>-0.5827234859492947</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1238367309693444</v>
+        <v>0.1491660793986469</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.02116251158336979</v>
+        <v>-0.01136694070685706</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.663834348918741</v>
+        <v>-1.693373525834261</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.085756348914245</v>
+        <v>-1.116283580642033</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.263721935154244</v>
+        <v>-1.294022883079926</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.4454621640443435</v>
+        <v>0.4713566848138839</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.628894060307239</v>
+        <v>0.7155168958191354</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>1.043850097947768</v>
+        <v>1.069519347226439</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.17984493738129</v>
+        <v>0.1456876456876444</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.157132724458819</v>
+        <v>-0.1906586410873956</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.363571756414629</v>
+        <v>-0.3967139198073681</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-1.060169475460178</v>
+        <v>-1.091753712972107</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.3439624210166414</v>
+        <v>0.3700675880968305</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.5105373534568756</v>
+        <v>0.5979836769337439</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.6989674109004298</v>
+        <v>0.7249774721169331</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.2225074882327789</v>
+        <v>0.1880931582298189</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.7562949276758033</v>
+        <v>0.720780174783421</v>
       </c>
     </row>
     <row r="12">
@@ -4290,79 +4290,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.8297513179334501</v>
+        <v>0.8954432091486808</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.6214719117944938</v>
+        <v>0.6614728624117703</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.020671834625325</v>
+        <v>-0.9781590898450361</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.6235662821879728</v>
+        <v>-0.5822421415458408</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.5262044529060219</v>
+        <v>0.4932577084875405</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.3093783338182519</v>
+        <v>0.3340641016094281</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.6657377029903202</v>
+        <v>-0.5827234859492947</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.1238367309693444</v>
+        <v>0.1491660793986469</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.02116251158336979</v>
+        <v>-0.01136694070685706</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.663834348918741</v>
+        <v>-1.693373525834261</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.085756348914245</v>
+        <v>-1.116283580642033</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.263721935154244</v>
+        <v>-1.294022883079926</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4454621640443435</v>
+        <v>0.4713566848138839</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.628894060307239</v>
+        <v>0.7155168958191354</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1.043850097947768</v>
+        <v>1.069519347226439</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.17984493738129</v>
+        <v>0.1456876456876444</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.157132724458819</v>
+        <v>-0.1906586410873956</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.363571756414629</v>
+        <v>-0.3967139198073681</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.060169475460178</v>
+        <v>-1.091753712972107</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.3439624210166414</v>
+        <v>0.3700675880968305</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.5105373534568756</v>
+        <v>0.5979836769337439</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.6989674109004298</v>
+        <v>0.7249774721169331</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.2225074882327789</v>
+        <v>0.1880931582298189</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.7562949276758033</v>
+        <v>0.720780174783421</v>
       </c>
     </row>
     <row r="13">
@@ -4372,79 +4372,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.8297513179334501</v>
+        <v>0.8954432091486808</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.6214719117944938</v>
+        <v>0.6614728624117703</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.020671834625325</v>
+        <v>-0.9781590898450361</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.6235662821879728</v>
+        <v>-0.5822421415458408</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.5262044529060219</v>
+        <v>0.4932577084875405</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.3093783338182519</v>
+        <v>0.3340641016094281</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.6657377029903202</v>
+        <v>-0.5827234859492947</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1238367309693444</v>
+        <v>0.1491660793986469</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.02116251158336979</v>
+        <v>-0.01136694070685706</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.663834348918741</v>
+        <v>-1.693373525834261</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.085756348914245</v>
+        <v>-1.116283580642033</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.263721935154244</v>
+        <v>-1.294022883079926</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.4454621640443435</v>
+        <v>0.4713566848138839</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.628894060307239</v>
+        <v>0.7155168958191354</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.043850097947768</v>
+        <v>1.069519347226439</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.17984493738129</v>
+        <v>0.1456876456876444</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.157132724458819</v>
+        <v>-0.1906586410873956</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.363571756414629</v>
+        <v>-0.3967139198073681</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.060169475460178</v>
+        <v>-1.091753712972107</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.3439624210166414</v>
+        <v>0.3700675880968305</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.5105373534568756</v>
+        <v>0.5979836769337439</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.6989674109004298</v>
+        <v>0.7249774721169331</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.2225074882327789</v>
+        <v>0.1880931582298189</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.7562949276758033</v>
+        <v>0.720780174783421</v>
       </c>
     </row>
     <row r="14">
@@ -4454,79 +4454,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.8297513179334501</v>
+        <v>0.8954432091486808</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.6214719117944938</v>
+        <v>0.6614728624117703</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.020671834625325</v>
+        <v>-0.9781590898450361</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.6235662821879728</v>
+        <v>-0.5822421415458408</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.5262044529060219</v>
+        <v>0.4932577084875405</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3093783338182519</v>
+        <v>0.3340641016094281</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.6657377029903202</v>
+        <v>-0.5827234859492947</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.1238367309693444</v>
+        <v>0.1491660793986469</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.02116251158336979</v>
+        <v>-0.01136694070685706</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.663834348918741</v>
+        <v>-1.693373525834261</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.085756348914245</v>
+        <v>-1.116283580642033</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.263721935154244</v>
+        <v>-1.294022883079926</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.4454621640443435</v>
+        <v>0.4713566848138839</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.628894060307239</v>
+        <v>0.7155168958191354</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1.043850097947768</v>
+        <v>1.069519347226439</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.17984493738129</v>
+        <v>0.1456876456876444</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.157132724458819</v>
+        <v>-0.1906586410873956</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.363571756414629</v>
+        <v>-0.3967139198073681</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.060169475460178</v>
+        <v>-1.091753712972107</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.3439624210166414</v>
+        <v>0.3700675880968305</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.5105373534568756</v>
+        <v>0.5979836769337439</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.6989674109004298</v>
+        <v>0.7249774721169331</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.2225074882327789</v>
+        <v>0.1880931582298189</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.7562949276758033</v>
+        <v>0.720780174783421</v>
       </c>
     </row>
     <row r="15">
@@ -4536,79 +4536,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.8297513179334501</v>
+        <v>0.8954432091486808</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.6214719117944938</v>
+        <v>0.6614728624117703</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.020671834625325</v>
+        <v>-0.9781590898450361</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.6235662821879728</v>
+        <v>-0.5822421415458408</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.5262044529060219</v>
+        <v>0.4932577084875405</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3093783338182519</v>
+        <v>0.3340641016094281</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.6657377029903202</v>
+        <v>-0.5827234859492947</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1238367309693444</v>
+        <v>0.1491660793986469</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.02116251158336979</v>
+        <v>-0.01136694070685706</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.663834348918741</v>
+        <v>-1.693373525834261</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.085756348914245</v>
+        <v>-1.116283580642033</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.263721935154244</v>
+        <v>-1.294022883079926</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.4454621640443435</v>
+        <v>0.4713566848138839</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.628894060307239</v>
+        <v>0.7155168958191354</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.043850097947768</v>
+        <v>1.069519347226439</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.17984493738129</v>
+        <v>0.1456876456876444</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.157132724458819</v>
+        <v>-0.1906586410873956</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.363571756414629</v>
+        <v>-0.3967139198073681</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.060169475460178</v>
+        <v>-1.091753712972107</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.3439624210166414</v>
+        <v>0.3700675880968305</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.5105373534568756</v>
+        <v>0.5979836769337439</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.6989674109004298</v>
+        <v>0.7249774721169331</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.2225074882327789</v>
+        <v>0.1880931582298189</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.7562949276758033</v>
+        <v>0.720780174783421</v>
       </c>
     </row>
     <row r="16">
@@ -4618,79 +4618,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.6462016590248041</v>
+        <v>0.7274324564605053</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.01825872793614991</v>
+        <v>-0.01057014834091774</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.3809411948946888</v>
+        <v>-0.3733203801676126</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.229626888248582</v>
+        <v>-1.220683001760889</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.08849401519558597</v>
+        <v>0.09443837100353392</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1956721712322533</v>
+        <v>-0.1515989248480736</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.2570688037553808</v>
+        <v>-0.2123531155789209</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1095187476504762</v>
+        <v>0.1154960457286052</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.4174339796446915</v>
+        <v>-0.449077378417293</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.461405199121167</v>
+        <v>-1.49135332381406</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.7146362409520322</v>
+        <v>-0.7459132102716595</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.5889581024956669</v>
+        <v>-0.5819152841798712</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.4454621640443435</v>
+        <v>0.4914700423332405</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.7370111821775183</v>
+        <v>0.7829932790849981</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.5239837270175656</v>
+        <v>0.5297082810995732</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.192027949704574</v>
+        <v>-0.2254324622745614</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.664232115939555</v>
+        <v>-0.6967315155813267</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.2283452520197713</v>
+        <v>-0.2617611532756499</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.891136344966597</v>
+        <v>-0.8835154889906036</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.1631369704640804</v>
+        <v>-0.1165284304140854</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.05749630861044608</v>
+        <v>-0.01053559284313366</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.1606430630675888</v>
+        <v>-0.1539948064496599</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.1547568107260062</v>
+        <v>0.1204799060323936</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.05671320240550415</v>
+        <v>-0.09057885158575374</v>
       </c>
     </row>
     <row r="17">
@@ -4700,79 +4700,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6462016590248041</v>
+        <v>0.7274324564605053</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.01825872793614991</v>
+        <v>-0.01057014834091774</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.3809411948946888</v>
+        <v>-0.3733203801676126</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.229626888248582</v>
+        <v>-1.220683001760889</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.08849401519558597</v>
+        <v>0.09443837100353392</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.1956721712322533</v>
+        <v>-0.1515989248480736</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.2570688037553808</v>
+        <v>-0.2123531155789209</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.1095187476504762</v>
+        <v>0.1154960457286052</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.4174339796446915</v>
+        <v>-0.449077378417293</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.461405199121167</v>
+        <v>-1.49135332381406</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.7146362409520322</v>
+        <v>-0.7459132102716595</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.5889581024956669</v>
+        <v>-0.5819152841798712</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.4454621640443435</v>
+        <v>0.4914700423332405</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.7370111821775183</v>
+        <v>0.7829932790849981</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.5239837270175656</v>
+        <v>0.5297082810995732</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.192027949704574</v>
+        <v>-0.2254324622745614</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.664232115939555</v>
+        <v>-0.6967315155813267</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.2283452520197713</v>
+        <v>-0.2617611532756499</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.891136344966597</v>
+        <v>-0.8835154889906036</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.1631369704640804</v>
+        <v>-0.1165284304140854</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.05749630861044608</v>
+        <v>-0.01053559284313366</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.1606430630675888</v>
+        <v>-0.1539948064496599</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.1547568107260062</v>
+        <v>0.1204799060323936</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.05671320240550415</v>
+        <v>-0.09057885158575374</v>
       </c>
     </row>
     <row r="18">
@@ -4782,79 +4782,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.6462016590248041</v>
+        <v>0.7274324564605053</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.01825872793614991</v>
+        <v>-0.01057014834091774</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.3809411948946888</v>
+        <v>-0.3733203801676126</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.229626888248582</v>
+        <v>-1.220683001760889</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.08849401519558597</v>
+        <v>0.09443837100353392</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.1956721712322533</v>
+        <v>-0.1515989248480736</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.2570688037553808</v>
+        <v>-0.2123531155789209</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.1095187476504762</v>
+        <v>0.1154960457286052</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.4174339796446915</v>
+        <v>-0.449077378417293</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.461405199121167</v>
+        <v>-1.49135332381406</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7146362409520322</v>
+        <v>-0.7459132102716595</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.5889581024956669</v>
+        <v>-0.5819152841798712</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.4454621640443435</v>
+        <v>0.4914700423332405</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.7370111821775183</v>
+        <v>0.7829932790849981</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.5239837270175656</v>
+        <v>0.5297082810995732</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.192027949704574</v>
+        <v>-0.2254324622745614</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.664232115939555</v>
+        <v>-0.6967315155813267</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.2283452520197713</v>
+        <v>-0.2617611532756499</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.891136344966597</v>
+        <v>-0.8835154889906036</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.1631369704640804</v>
+        <v>-0.1165284304140854</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.05749630861044608</v>
+        <v>-0.01053559284313366</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.1606430630675888</v>
+        <v>-0.1539948064496599</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.1547568107260062</v>
+        <v>0.1204799060323936</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.05671320240550415</v>
+        <v>-0.09057885158575374</v>
       </c>
     </row>
     <row r="19">
@@ -4864,79 +4864,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.6462016590248041</v>
+        <v>0.7274324564605053</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.01825872793614991</v>
+        <v>-0.01057014834091774</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.3809411948946888</v>
+        <v>-0.3733203801676126</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.229626888248582</v>
+        <v>-1.220683001760889</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.08849401519558597</v>
+        <v>0.09443837100353392</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1956721712322533</v>
+        <v>-0.1515989248480736</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.2570688037553808</v>
+        <v>-0.2123531155789209</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.1095187476504762</v>
+        <v>0.1154960457286052</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.4174339796446915</v>
+        <v>-0.449077378417293</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.461405199121167</v>
+        <v>-1.49135332381406</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.7146362409520322</v>
+        <v>-0.7459132102716595</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.5889581024956669</v>
+        <v>-0.5819152841798712</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.4454621640443435</v>
+        <v>0.4914700423332405</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.7370111821775183</v>
+        <v>0.7829932790849981</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.5239837270175656</v>
+        <v>0.5297082810995732</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.192027949704574</v>
+        <v>-0.2254324622745614</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.664232115939555</v>
+        <v>-0.6967315155813267</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.2283452520197713</v>
+        <v>-0.2617611532756499</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.891136344966597</v>
+        <v>-0.8835154889906036</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.1631369704640804</v>
+        <v>-0.1165284304140854</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.05749630861044608</v>
+        <v>-0.01053559284313366</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.1606430630675888</v>
+        <v>-0.1539948064496599</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.1547568107260062</v>
+        <v>0.1204799060323936</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.05671320240550415</v>
+        <v>-0.09057885158575374</v>
       </c>
     </row>
     <row r="20">
@@ -4946,79 +4946,79 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6462016590248041</v>
+        <v>0.7274324564605053</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.01825872793614991</v>
+        <v>-0.01057014834091774</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.3809411948946888</v>
+        <v>-0.3733203801676126</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.229626888248582</v>
+        <v>-1.220683001760889</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.08849401519558597</v>
+        <v>0.09443837100353392</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1956721712322533</v>
+        <v>-0.1515989248480736</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.2570688037553808</v>
+        <v>-0.2123531155789209</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.1095187476504762</v>
+        <v>0.1154960457286052</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.4174339796446915</v>
+        <v>-0.449077378417293</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.461405199121167</v>
+        <v>-1.49135332381406</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7146362409520322</v>
+        <v>-0.7459132102716595</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.5889581024956669</v>
+        <v>-0.5819152841798712</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.4454621640443435</v>
+        <v>0.4914700423332405</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.7370111821775183</v>
+        <v>0.7829932790849981</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.5239837270175656</v>
+        <v>0.5297082810995732</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.192027949704574</v>
+        <v>-0.2254324622745614</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.664232115939555</v>
+        <v>-0.6967315155813267</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.2283452520197713</v>
+        <v>-0.2617611532756499</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.891136344966597</v>
+        <v>-0.8835154889906036</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.1631369704640804</v>
+        <v>-0.1165284304140854</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.05749630861044608</v>
+        <v>-0.01053559284313366</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.1606430630675888</v>
+        <v>-0.1539948064496599</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.1547568107260062</v>
+        <v>0.1204799060323936</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.05671320240550415</v>
+        <v>-0.09057885158575374</v>
       </c>
     </row>
     <row r="21">
@@ -5028,79 +5028,79 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1962</v>
+        <v>1966</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.6684515184724802</v>
+        <v>0.7069789735245493</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.1242835148119923</v>
+        <v>-0.1333589977271785</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.6018943945712891</v>
+        <v>-0.610811818244521</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.062607146760755</v>
+        <v>-1.043137192698602</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.04111035079063896</v>
+        <v>0.06595262816887271</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2498377499796902</v>
+        <v>-0.2247883553130023</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.03099268690656487</v>
+        <v>-0.005829930332332367</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.2806635073190122</v>
+        <v>-0.2840413750854083</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.5654709991751687</v>
+        <v>-0.5971641222487278</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.8826838937100447</v>
+        <v>-0.9141527466134818</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.4052039331227135</v>
+        <v>-0.4083937343842194</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2782927237031245</v>
+        <v>-0.2523690219534487</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.2514632784841453</v>
+        <v>0.2773402103425369</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.4159731557945605</v>
+        <v>0.4417751419812035</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.09233448753914075</v>
+        <v>0.08820037231942734</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.1973585977669359</v>
+        <v>-0.2311182894939208</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.2806318031164921</v>
+        <v>-0.3142740051515958</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.1313274572847902</v>
+        <v>-0.1350673041472277</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.7289814700373682</v>
+        <v>-0.7019130230672346</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.4610481854897088</v>
+        <v>-0.4343398870155752</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.1597426976042158</v>
+        <v>-0.1331061069996125</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.04943843448133833</v>
+        <v>0.04537143108263564</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.05284618273512365</v>
+        <v>-0.08707145562147645</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.0778464412608173</v>
+        <v>-0.112039008946482</v>
       </c>
     </row>
     <row r="22">
@@ -5110,79 +5110,79 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1962</v>
+        <v>1966</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.6684515184724802</v>
+        <v>0.7069789735245493</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.1242835148119923</v>
+        <v>-0.1333589977271785</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.6018943945712891</v>
+        <v>-0.610811818244521</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.062607146760755</v>
+        <v>-1.043137192698602</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.04111035079063896</v>
+        <v>0.06595262816887271</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.2498377499796902</v>
+        <v>-0.2247883553130023</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.03099268690656487</v>
+        <v>-0.005829930332332367</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.2806635073190122</v>
+        <v>-0.2840413750854083</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.5654709991751687</v>
+        <v>-0.5971641222487278</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.8826838937100447</v>
+        <v>-0.9141527466134818</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.4052039331227135</v>
+        <v>-0.4083937343842194</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2782927237031245</v>
+        <v>-0.2523690219534487</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.2514632784841453</v>
+        <v>0.2773402103425369</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.4159731557945605</v>
+        <v>0.4417751419812035</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.09233448753914075</v>
+        <v>0.08820037231942734</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.1973585977669359</v>
+        <v>-0.2311182894939208</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.2806318031164921</v>
+        <v>-0.3142740051515958</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.1313274572847902</v>
+        <v>-0.1350673041472277</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.7289814700373682</v>
+        <v>-0.7019130230672346</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.4610481854897088</v>
+        <v>-0.4343398870155752</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.1597426976042158</v>
+        <v>-0.1331061069996125</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.04943843448133833</v>
+        <v>0.04537143108263564</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.05284618273512365</v>
+        <v>-0.08707145562147645</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.0778464412608173</v>
+        <v>-0.112039008946482</v>
       </c>
     </row>
     <row r="23">
@@ -5192,79 +5192,79 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1962</v>
+        <v>1966</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.6684515184724802</v>
+        <v>0.7069789735245493</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.1242835148119923</v>
+        <v>-0.1333589977271785</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.6018943945712891</v>
+        <v>-0.610811818244521</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.062607146760755</v>
+        <v>-1.043137192698602</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.04111035079063896</v>
+        <v>0.06595262816887271</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2498377499796902</v>
+        <v>-0.2247883553130023</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.03099268690656487</v>
+        <v>-0.005829930332332367</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.2806635073190122</v>
+        <v>-0.2840413750854083</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.5654709991751687</v>
+        <v>-0.5971641222487278</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.8826838937100447</v>
+        <v>-0.9141527466134818</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4052039331227135</v>
+        <v>-0.4083937343842194</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.2782927237031245</v>
+        <v>-0.2523690219534487</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.2514632784841453</v>
+        <v>0.2773402103425369</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.4159731557945605</v>
+        <v>0.4417751419812035</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.09233448753914075</v>
+        <v>0.08820037231942734</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.1973585977669359</v>
+        <v>-0.2311182894939208</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.2806318031164921</v>
+        <v>-0.3142740051515958</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.1313274572847902</v>
+        <v>-0.1350673041472277</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.7289814700373682</v>
+        <v>-0.7019130230672346</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.4610481854897088</v>
+        <v>-0.4343398870155752</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.1597426976042158</v>
+        <v>-0.1331061069996125</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>0.04943843448133833</v>
+        <v>0.04537143108263564</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.05284618273512365</v>
+        <v>-0.08707145562147645</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.0778464412608173</v>
+        <v>-0.112039008946482</v>
       </c>
     </row>
     <row r="24">
@@ -5274,79 +5274,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1962</v>
+        <v>1966</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.6684515184724802</v>
+        <v>0.7069789735245493</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.1242835148119923</v>
+        <v>-0.1333589977271785</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.6018943945712891</v>
+        <v>-0.610811818244521</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.062607146760755</v>
+        <v>-1.043137192698602</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.04111035079063896</v>
+        <v>0.06595262816887271</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2498377499796902</v>
+        <v>-0.2247883553130023</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.03099268690656487</v>
+        <v>-0.005829930332332367</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2806635073190122</v>
+        <v>-0.2840413750854083</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.5654709991751687</v>
+        <v>-0.5971641222487278</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.8826838937100447</v>
+        <v>-0.9141527466134818</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.4052039331227135</v>
+        <v>-0.4083937343842194</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.2782927237031245</v>
+        <v>-0.2523690219534487</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.2514632784841453</v>
+        <v>0.2773402103425369</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.4159731557945605</v>
+        <v>0.4417751419812035</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.09233448753914075</v>
+        <v>0.08820037231942734</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.1973585977669359</v>
+        <v>-0.2311182894939208</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.2806318031164921</v>
+        <v>-0.3142740051515958</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.1313274572847902</v>
+        <v>-0.1350673041472277</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.7289814700373682</v>
+        <v>-0.7019130230672346</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.4610481854897088</v>
+        <v>-0.4343398870155752</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.1597426976042158</v>
+        <v>-0.1331061069996125</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.04943843448133833</v>
+        <v>0.04537143108263564</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.05284618273512365</v>
+        <v>-0.08707145562147645</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.0778464412608173</v>
+        <v>-0.112039008946482</v>
       </c>
     </row>
     <row r="25">
@@ -5356,79 +5356,79 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1962</v>
+        <v>1966</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.6684515184724802</v>
+        <v>0.7069789735245493</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.1242835148119923</v>
+        <v>-0.1333589977271785</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.6018943945712891</v>
+        <v>-0.610811818244521</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.062607146760755</v>
+        <v>-1.043137192698602</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.04111035079063896</v>
+        <v>0.06595262816887271</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.2498377499796902</v>
+        <v>-0.2247883553130023</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.03099268690656487</v>
+        <v>-0.005829930332332367</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.2806635073190122</v>
+        <v>-0.2840413750854083</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.5654709991751687</v>
+        <v>-0.5971641222487278</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.8826838937100447</v>
+        <v>-0.9141527466134818</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.4052039331227135</v>
+        <v>-0.4083937343842194</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.2782927237031245</v>
+        <v>-0.2523690219534487</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.2514632784841453</v>
+        <v>0.2773402103425369</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.4159731557945605</v>
+        <v>0.4417751419812035</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.09233448753914075</v>
+        <v>0.08820037231942734</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.1973585977669359</v>
+        <v>-0.2311182894939208</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.2806318031164921</v>
+        <v>-0.3142740051515958</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.1313274572847902</v>
+        <v>-0.1350673041472277</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.7289814700373682</v>
+        <v>-0.7019130230672346</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.4610481854897088</v>
+        <v>-0.4343398870155752</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.1597426976042158</v>
+        <v>-0.1331061069996125</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.04943843448133833</v>
+        <v>0.04537143108263564</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.05284618273512365</v>
+        <v>-0.08707145562147645</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.0778464412608173</v>
+        <v>-0.112039008946482</v>
       </c>
     </row>
     <row r="26">
@@ -5438,79 +5438,79 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2448</v>
+        <v>2452</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.373324743240488</v>
+        <v>-0.3588373889587118</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.4318136847310541</v>
+        <v>-0.4505023558660568</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.491506859662536</v>
+        <v>-0.4886328270470699</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.7995034861397983</v>
+        <v>-0.7737989267275296</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.07613101339310191</v>
+        <v>0.08933668512825221</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.07935253439249834</v>
+        <v>-0.06600568228981984</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.3824166879619852</v>
+        <v>-0.3685230159631914</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.475311853850009</v>
+        <v>-0.4843308878376718</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.2478920174600177</v>
+        <v>-0.2804401330443653</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.3710219837754209</v>
+        <v>-0.3803242680246441</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.2186381559855946</v>
+        <v>-0.2047300116321367</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.3115551935138186</v>
+        <v>-0.2974720084802698</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.1751170454221835</v>
+        <v>0.1888674405815749</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.05937139731261709</v>
+        <v>0.0733108298624856</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.249491459660554</v>
+        <v>-0.259364607669248</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.2821054499822822</v>
+        <v>-0.3159134058239061</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.2531777213124471</v>
+        <v>-0.262954766015099</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.1543648325750482</v>
+        <v>-0.1400509017008389</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.4848226128584656</v>
+        <v>-0.4701601709154914</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.3552181924350037</v>
+        <v>-0.3407624443791519</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.1806080702298516</v>
+        <v>-0.1662417737087196</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.1505246639752613</v>
+        <v>-0.1605549181589936</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.1371689026487815</v>
+        <v>-0.1714450650328345</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>0.1136598248541816</v>
+        <v>0.1032439663978266</v>
       </c>
     </row>
     <row r="27">
@@ -5520,79 +5520,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2448</v>
+        <v>2452</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.373324743240488</v>
+        <v>-0.3588373889587118</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4318136847310541</v>
+        <v>-0.4505023558660568</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.491506859662536</v>
+        <v>-0.4886328270470699</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.7995034861397983</v>
+        <v>-0.7737989267275296</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.07613101339310191</v>
+        <v>0.08933668512825221</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.07935253439249834</v>
+        <v>-0.06600568228981984</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.3824166879619852</v>
+        <v>-0.3685230159631914</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.475311853850009</v>
+        <v>-0.4843308878376718</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2478920174600177</v>
+        <v>-0.2804401330443653</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.3710219837754209</v>
+        <v>-0.3803242680246441</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.2186381559855946</v>
+        <v>-0.2047300116321367</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.3115551935138186</v>
+        <v>-0.2974720084802698</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.1751170454221835</v>
+        <v>0.1888674405815749</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.05937139731261709</v>
+        <v>0.0733108298624856</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.249491459660554</v>
+        <v>-0.259364607669248</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.2821054499822822</v>
+        <v>-0.3159134058239061</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.2531777213124471</v>
+        <v>-0.262954766015099</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.1543648325750482</v>
+        <v>-0.1400509017008389</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.4848226128584656</v>
+        <v>-0.4701601709154914</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.3552181924350037</v>
+        <v>-0.3407624443791519</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.1806080702298516</v>
+        <v>-0.1662417737087196</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.1505246639752613</v>
+        <v>-0.1605549181589936</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.1371689026487815</v>
+        <v>-0.1714450650328345</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>0.1136598248541816</v>
+        <v>0.1032439663978266</v>
       </c>
     </row>
     <row r="28">
@@ -5602,79 +5602,79 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2448</v>
+        <v>2452</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.373324743240488</v>
+        <v>-0.3588373889587118</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4318136847310541</v>
+        <v>-0.4505023558660568</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.491506859662536</v>
+        <v>-0.4886328270470699</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.7995034861397983</v>
+        <v>-0.7737989267275296</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.07613101339310191</v>
+        <v>0.08933668512825221</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.07935253439249834</v>
+        <v>-0.06600568228981984</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.3824166879619852</v>
+        <v>-0.3685230159631914</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.475311853850009</v>
+        <v>-0.4843308878376718</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.2478920174600177</v>
+        <v>-0.2804401330443653</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.3710219837754209</v>
+        <v>-0.3803242680246441</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.2186381559855946</v>
+        <v>-0.2047300116321367</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.3115551935138186</v>
+        <v>-0.2974720084802698</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.1751170454221835</v>
+        <v>0.1888674405815749</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.05937139731261709</v>
+        <v>0.0733108298624856</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.249491459660554</v>
+        <v>-0.259364607669248</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.2821054499822822</v>
+        <v>-0.3159134058239061</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.2531777213124471</v>
+        <v>-0.262954766015099</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.1543648325750482</v>
+        <v>-0.1400509017008389</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.4848226128584656</v>
+        <v>-0.4701601709154914</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3552181924350037</v>
+        <v>-0.3407624443791519</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.1806080702298516</v>
+        <v>-0.1662417737087196</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.1505246639752613</v>
+        <v>-0.1605549181589936</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.1371689026487815</v>
+        <v>-0.1714450650328345</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>0.1136598248541816</v>
+        <v>0.1032439663978266</v>
       </c>
     </row>
     <row r="29">
@@ -5684,79 +5684,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2448</v>
+        <v>2452</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.373324743240488</v>
+        <v>-0.3588373889587118</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.4318136847310541</v>
+        <v>-0.4505023558660568</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.491506859662536</v>
+        <v>-0.4886328270470699</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.7995034861397983</v>
+        <v>-0.7737989267275296</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.07613101339310191</v>
+        <v>0.08933668512825221</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.07935253439249834</v>
+        <v>-0.06600568228981984</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.3824166879619852</v>
+        <v>-0.3685230159631914</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.475311853850009</v>
+        <v>-0.4843308878376718</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.2478920174600177</v>
+        <v>-0.2804401330443653</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.3710219837754209</v>
+        <v>-0.3803242680246441</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.2186381559855946</v>
+        <v>-0.2047300116321367</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.3115551935138186</v>
+        <v>-0.2974720084802698</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.1751170454221835</v>
+        <v>0.1888674405815749</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.05937139731261709</v>
+        <v>0.0733108298624856</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.249491459660554</v>
+        <v>-0.259364607669248</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.2821054499822822</v>
+        <v>-0.3159134058239061</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.2531777213124471</v>
+        <v>-0.262954766015099</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.1543648325750482</v>
+        <v>-0.1400509017008389</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.4848226128584656</v>
+        <v>-0.4701601709154914</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.3552181924350037</v>
+        <v>-0.3407624443791519</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.1806080702298516</v>
+        <v>-0.1662417737087196</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.1505246639752613</v>
+        <v>-0.1605549181589936</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.1371689026487815</v>
+        <v>-0.1714450650328345</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.1136598248541816</v>
+        <v>0.1032439663978266</v>
       </c>
     </row>
     <row r="30">
@@ -5766,79 +5766,79 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2448</v>
+        <v>2452</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.373324743240488</v>
+        <v>-0.3588373889587118</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.4318136847310541</v>
+        <v>-0.4505023558660568</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.491506859662536</v>
+        <v>-0.4886328270470699</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.7995034861397983</v>
+        <v>-0.7737989267275296</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.07613101339310191</v>
+        <v>0.08933668512825221</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.07935253439249834</v>
+        <v>-0.06600568228981984</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.3824166879619852</v>
+        <v>-0.3685230159631914</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.475311853850009</v>
+        <v>-0.4843308878376718</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.2478920174600177</v>
+        <v>-0.2804401330443653</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.3710219837754209</v>
+        <v>-0.3803242680246441</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.2186381559855946</v>
+        <v>-0.2047300116321367</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.3115551935138186</v>
+        <v>-0.2974720084802698</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.1751170454221835</v>
+        <v>0.1888674405815749</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.05937139731261709</v>
+        <v>0.0733108298624856</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.249491459660554</v>
+        <v>-0.259364607669248</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.2821054499822822</v>
+        <v>-0.3159134058239061</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.2531777213124471</v>
+        <v>-0.262954766015099</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.1543648325750482</v>
+        <v>-0.1400509017008389</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.4848226128584656</v>
+        <v>-0.4701601709154914</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.3552181924350037</v>
+        <v>-0.3407624443791519</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.1806080702298516</v>
+        <v>-0.1662417737087196</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.1505246639752613</v>
+        <v>-0.1605549181589936</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.1371689026487815</v>
+        <v>-0.1714450650328345</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.1136598248541816</v>
+        <v>0.1032439663978266</v>
       </c>
     </row>
     <row r="31">
@@ -5848,79 +5848,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2934</v>
+        <v>2938</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1896160120800161</v>
+        <v>-0.192571251363006</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1293287780305903</v>
+        <v>-0.137274233053347</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2483141110480815</v>
+        <v>-0.2377295643310404</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.3336457279502412</v>
+        <v>-0.3228744760253974</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.0317685686396203</v>
+        <v>0.03727402316200568</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.100930245361134</v>
+        <v>-0.09526549291604169</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.4139662571890241</v>
+        <v>-0.4078035549318031</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.1983019763517433</v>
+        <v>-0.2117602571374491</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.06630709794352896</v>
+        <v>0.05240188958178749</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.1307049564260723</v>
+        <v>-0.1248064996401155</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.1082194545691948</v>
+        <v>-0.1023805626698362</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.02810650653251656</v>
+        <v>-0.0223509397661914</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.05608009914320178</v>
+        <v>0.06182983311674661</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.043209248741924</v>
+        <v>-0.03730515617752417</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1380911326091478</v>
+        <v>-0.1523391530113116</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.1346946715657396</v>
+        <v>-0.148814117404946</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.1327781550448535</v>
+        <v>-0.1267119327613955</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.1154571170987708</v>
+        <v>-0.1094062206213451</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.2874038541063584</v>
+        <v>-0.2811426273959015</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.1482192355563754</v>
+        <v>-0.1421678066144878</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.194565696877234</v>
+        <v>-0.1883998419910711</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.04576403783226368</v>
+        <v>-0.06016417074710745</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>0.07910881498224143</v>
+        <v>0.06455346299326692</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.03722331978180904</v>
+        <v>0.04308274431713954</v>
       </c>
     </row>
     <row r="32">
@@ -5930,79 +5930,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2934</v>
+        <v>2938</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1896160120800161</v>
+        <v>-0.192571251363006</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1293287780305903</v>
+        <v>-0.137274233053347</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2483141110480815</v>
+        <v>-0.2377295643310404</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3336457279502412</v>
+        <v>-0.3228744760253974</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.0317685686396203</v>
+        <v>0.03727402316200568</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.100930245361134</v>
+        <v>-0.09526549291604169</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4139662571890241</v>
+        <v>-0.4078035549318031</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.1983019763517433</v>
+        <v>-0.2117602571374491</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.06630709794352896</v>
+        <v>0.05240188958178749</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1307049564260723</v>
+        <v>-0.1248064996401155</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1082194545691948</v>
+        <v>-0.1023805626698362</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.02810650653251656</v>
+        <v>-0.0223509397661914</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.05608009914320178</v>
+        <v>0.06182983311674661</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.043209248741924</v>
+        <v>-0.03730515617752417</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.1380911326091478</v>
+        <v>-0.1523391530113116</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.1346946715657396</v>
+        <v>-0.148814117404946</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.1327781550448535</v>
+        <v>-0.1267119327613955</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.1154571170987708</v>
+        <v>-0.1094062206213451</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.2874038541063584</v>
+        <v>-0.2811426273959015</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.1482192355563754</v>
+        <v>-0.1421678066144878</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.194565696877234</v>
+        <v>-0.1883998419910711</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.04576403783226368</v>
+        <v>-0.06016417074710745</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>0.07910881498224143</v>
+        <v>0.06455346299326692</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.03722331978180904</v>
+        <v>0.04308274431713954</v>
       </c>
     </row>
     <row r="33">
@@ -6012,79 +6012,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2934</v>
+        <v>2938</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1896160120800161</v>
+        <v>-0.192571251363006</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1293287780305903</v>
+        <v>-0.137274233053347</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2483141110480815</v>
+        <v>-0.2377295643310404</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3336457279502412</v>
+        <v>-0.3228744760253974</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.0317685686396203</v>
+        <v>0.03727402316200568</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.100930245361134</v>
+        <v>-0.09526549291604169</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.4139662571890241</v>
+        <v>-0.4078035549318031</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.1983019763517433</v>
+        <v>-0.2117602571374491</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.06630709794352896</v>
+        <v>0.05240188958178749</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1307049564260723</v>
+        <v>-0.1248064996401155</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1082194545691948</v>
+        <v>-0.1023805626698362</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.02810650653251656</v>
+        <v>-0.0223509397661914</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.05608009914320178</v>
+        <v>0.06182983311674661</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.043209248741924</v>
+        <v>-0.03730515617752417</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.1380911326091478</v>
+        <v>-0.1523391530113116</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.1346946715657396</v>
+        <v>-0.148814117404946</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.1327781550448535</v>
+        <v>-0.1267119327613955</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.1154571170987708</v>
+        <v>-0.1094062206213451</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.2874038541063584</v>
+        <v>-0.2811426273959015</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.1482192355563754</v>
+        <v>-0.1421678066144878</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.194565696877234</v>
+        <v>-0.1883998419910711</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.04576403783226368</v>
+        <v>-0.06016417074710745</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>0.07910881498224143</v>
+        <v>0.06455346299326692</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.03722331978180904</v>
+        <v>0.04308274431713954</v>
       </c>
     </row>
     <row r="34">
@@ -6094,79 +6094,79 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2934</v>
+        <v>2938</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1896160120800161</v>
+        <v>-0.192571251363006</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1293287780305903</v>
+        <v>-0.137274233053347</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2483141110480815</v>
+        <v>-0.2377295643310404</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.3336457279502412</v>
+        <v>-0.3228744760253974</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.0317685686396203</v>
+        <v>0.03727402316200568</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.100930245361134</v>
+        <v>-0.09526549291604169</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.4139662571890241</v>
+        <v>-0.4078035549318031</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.1983019763517433</v>
+        <v>-0.2117602571374491</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.06630709794352896</v>
+        <v>0.05240188958178749</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1307049564260723</v>
+        <v>-0.1248064996401155</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1082194545691948</v>
+        <v>-0.1023805626698362</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.02810650653251656</v>
+        <v>-0.0223509397661914</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.05608009914320178</v>
+        <v>0.06182983311674661</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.043209248741924</v>
+        <v>-0.03730515617752417</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.1380911326091478</v>
+        <v>-0.1523391530113116</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.1346946715657396</v>
+        <v>-0.148814117404946</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.1327781550448535</v>
+        <v>-0.1267119327613955</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.1154571170987708</v>
+        <v>-0.1094062206213451</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.2874038541063584</v>
+        <v>-0.2811426273959015</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.1482192355563754</v>
+        <v>-0.1421678066144878</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.194565696877234</v>
+        <v>-0.1883998419910711</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.04576403783226368</v>
+        <v>-0.06016417074710745</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>0.07910881498224143</v>
+        <v>0.06455346299326692</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>0.03722331978180904</v>
+        <v>0.04308274431713954</v>
       </c>
     </row>
     <row r="35">
@@ -6176,79 +6176,79 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2934</v>
+        <v>2938</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1896160120800161</v>
+        <v>-0.192571251363006</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1293287780305903</v>
+        <v>-0.137274233053347</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2483141110480815</v>
+        <v>-0.2377295643310404</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.3336457279502412</v>
+        <v>-0.3228744760253974</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.0317685686396203</v>
+        <v>0.03727402316200568</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.100930245361134</v>
+        <v>-0.09526549291604169</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4139662571890241</v>
+        <v>-0.4078035549318031</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1983019763517433</v>
+        <v>-0.2117602571374491</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.06630709794352896</v>
+        <v>0.05240188958178749</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1307049564260723</v>
+        <v>-0.1248064996401155</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1082194545691948</v>
+        <v>-0.1023805626698362</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.02810650653251656</v>
+        <v>-0.0223509397661914</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.05608009914320178</v>
+        <v>0.06182983311674661</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.043209248741924</v>
+        <v>-0.03730515617752417</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.1380911326091478</v>
+        <v>-0.1523391530113116</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.1346946715657396</v>
+        <v>-0.148814117404946</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.1327781550448535</v>
+        <v>-0.1267119327613955</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.1154571170987708</v>
+        <v>-0.1094062206213451</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.2874038541063584</v>
+        <v>-0.2811426273959015</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.1482192355563754</v>
+        <v>-0.1421678066144878</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.194565696877234</v>
+        <v>-0.1883998419910711</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.04576403783226368</v>
+        <v>-0.06016417074710745</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>0.07910881498224143</v>
+        <v>0.06455346299326692</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>0.03722331978180904</v>
+        <v>0.04308274431713954</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/time_of_day/time_of_day.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/time_of_day/time_of_day.xlsx
@@ -622,79 +622,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2.808438972354807</v>
+        <v>2.56752653374884</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.467239583839905</v>
+        <v>1.321068856781082</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.5748792128857971</v>
+        <v>-0.734558358962488</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.0782988300177081</v>
+        <v>-0.3251878003254944</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1910815828805923</v>
+        <v>0.2012641109369753</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0879794167907022</v>
+        <v>0.2694287536503666</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1244644086993816</v>
+        <v>0.4784556518556684</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.057455772448449</v>
+        <v>1.37759583526131</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.1123329573256839</v>
+        <v>0.100929074389235</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.693285013498219</v>
+        <v>-1.699012933034894</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.8136361225212809</v>
+        <v>-0.8248331313856809</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.6887411596769013</v>
+        <v>-0.9011645224990517</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.7332057715984703</v>
+        <v>0.7136367573128553</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.5122543321475206</v>
+        <v>0.4655278664022617</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>1.270757074512531</v>
+        <v>1.191479988499459</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.2467924368077306</v>
+        <v>0.1441694477405235</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.315409789638629</v>
+        <v>0.2415513564615708</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.2105896489261667</v>
+        <v>0.1086399668458142</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.02132805944100369</v>
+        <v>-0.07965184882041143</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.7339459509595656</v>
+        <v>0.6565995058981073</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.3944929089407125</v>
+        <v>0.2910583596796386</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.7242833434567331</v>
+        <v>0.61903082089988</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.7963147978127409</v>
+        <v>0.6614092119388886</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>1.329299444560299</v>
+        <v>1.104340669104651</v>
       </c>
     </row>
     <row r="7">
@@ -704,79 +704,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.390578777477991</v>
+        <v>0.5646424441680296</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.354009642080158</v>
+        <v>-1.282950660027886</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.8363200328717824</v>
+        <v>0.6681746824519834</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-2.498732446494373</v>
+        <v>-2.53064964384663</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.704008599165121</v>
+        <v>-0.889964517560621</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.122334122458184</v>
+        <v>-0.7332213966904462</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.5279218058601245</v>
+        <v>0.4782938336270206</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.04803897616153563</v>
+        <v>0.1735105280088405</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1.323743559109118</v>
+        <v>-1.504631958565248</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.087213530175688</v>
+        <v>-1.297388328067022</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.005380851093129024</v>
+        <v>-0.2223439249302785</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.8446799101367901</v>
+        <v>0.8229767185014651</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.5306070793693323</v>
+        <v>0.5122957103974173</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.9160572216128742</v>
+        <v>0.8669373932553199</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.5497898576194302</v>
+        <v>-0.6180574399083838</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.9671811148872891</v>
+        <v>-1.062460401812935</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-1.708827078582352</v>
+        <v>-1.770474674379116</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.008070449406986313</v>
+        <v>-0.09267986121788852</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.4647957746773912</v>
+        <v>-0.5636678789409331</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-1.089258185884979</v>
+        <v>-1.155543061831807</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-1.226055607392638</v>
+        <v>-1.319632562659621</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-1.910276315657178</v>
+        <v>-1.798156484789295</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.01477809512616091</v>
+        <v>-0.1447485356384632</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-1.713296904324089</v>
+        <v>-1.718239976056694</v>
       </c>
     </row>
     <row r="8">
@@ -786,79 +786,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.6432218785715662</v>
+        <v>0.7066977695712282</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.505879363094742</v>
+        <v>-0.549316347477216</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.331989951954654</v>
+        <v>-1.399481857544181</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.499935688510611</v>
+        <v>-0.6626476243536317</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.02077464033300913</v>
+        <v>0.2749081769589665</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.4460456394562442</v>
+        <v>-0.580601258730475</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.6203968953749666</v>
+        <v>0.8527655212934064</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.495425591895369</v>
+        <v>-1.67987088032362</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.045916172454348</v>
+        <v>-1.14722190826997</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.8386981169607068</v>
+        <v>0.6926343798383101</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.6185839028915794</v>
+        <v>0.676581354290029</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.7491445947073814</v>
+        <v>0.8059860207847223</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.3733863077767481</v>
+        <v>-0.3082851637764747</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.5944651842233384</v>
+        <v>-0.5565192252095841</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-1.251442582513228</v>
+        <v>-1.237457814293961</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.2480966436210608</v>
+        <v>-0.2705122667013384</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.8472042270949558</v>
+        <v>0.8447651622199643</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.2503720176311219</v>
+        <v>0.426355882297706</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.1479610574231387</v>
+        <v>0.03158303907284932</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-1.397116579838389</v>
+        <v>-1.17824803529102</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.5042938758185969</v>
+        <v>-0.5251484042018575</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.6501076015101788</v>
+        <v>0.6197900383819146</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.7169678992431443</v>
+        <v>-0.7647272221944803</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.1772126695964147</v>
+        <v>-0.1127278546454562</v>
       </c>
     </row>
     <row r="9">
@@ -868,79 +868,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-4.665044155328125</v>
+        <v>-4.55843178876745</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.734632732541478</v>
+        <v>-1.970924880079998</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.005579943072703486</v>
+        <v>-0.2764933857872194</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3151208111555448</v>
+        <v>0.5509827115506383</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.1838293161134033</v>
+        <v>0.2754245714513033</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.5752944797158577</v>
+        <v>0.4323581774494087</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.832646024215386</v>
+        <v>-1.985441887521681</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.294576327910988</v>
+        <v>-1.480758574924828</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.9985108332844277</v>
+        <v>0.8802796042380194</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.779055684299884</v>
+        <v>1.827214056142857</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.6186890969536023</v>
+        <v>0.6766848431049084</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.4797324376419425</v>
+        <v>-0.4129052414477101</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1684682749898982</v>
+        <v>-0.1050331312561568</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.414137315370887</v>
+        <v>-1.369527355290906</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-1.664027807373365</v>
+        <v>-1.646803912685158</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.6602126201097178</v>
+        <v>-0.6796033739844844</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.05535948655123235</v>
+        <v>-0.05144687712152063</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.1602001903724144</v>
+        <v>0.01933500549691303</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.4663688086217022</v>
+        <v>0.6411292082028197</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.03719819148501813</v>
+        <v>0.04105170214155152</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.3000091674460919</v>
+        <v>-0.1190608236790212</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.9928281597683295</v>
+        <v>-1.009897282778738</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.5133530687469019</v>
+        <v>-0.3591940485590186</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.9741211876466238</v>
+        <v>0.8245513340158013</v>
       </c>
     </row>
     <row r="10">
@@ -950,79 +950,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.6443360061069683</v>
+        <v>0.7080684142163136</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.443598992103709</v>
+        <v>1.383880229289005</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.028074830598285</v>
+        <v>1.346224666951159</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.95111263119643</v>
+        <v>2.173700764288988</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2251686388968537</v>
+        <v>-0.1302549417332983</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2427014303045851</v>
+        <v>-0.1761610923274972</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.6056521591847286</v>
+        <v>-0.7684033479679044</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.161003499864002</v>
+        <v>0.9547481393464068</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.732299229188783</v>
+        <v>1.810257421280895</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.164301585939214</v>
+        <v>1.217457958581882</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4137710641667027</v>
+        <v>0.4734328105846188</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.364529857440033</v>
+        <v>1.416363051235273</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.5783043405636263</v>
+        <v>-0.5115371962968283</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.5944651842233597</v>
+        <v>-0.5565192252095983</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.3861872608899191</v>
+        <v>0.3865968598177361</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.6945740775309446</v>
+        <v>0.8670974857236686</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.5606569405534714</v>
+        <v>0.7632170739986393</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.04513861866247737</v>
+        <v>0.01933500549691303</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.6717076176566366</v>
+        <v>0.6411292082027558</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.8585534276246563</v>
+        <v>0.8557156532617611</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.3000091674461132</v>
+        <v>-0.3227268114590984</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.4455839140805651</v>
+        <v>0.6207316840054489</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>1.255714757742368</v>
+        <v>1.190771960958301</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2604467135879389</v>
+        <v>-0.1958568292495428</v>
       </c>
     </row>
     <row r="11">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr"/>
@@ -1250,79 +1250,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2931</v>
+        <v>2953</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1714199146940913</v>
+        <v>0.1741576647585603</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.02437608821821868</v>
+        <v>-0.02002750728688341</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2323387278952609</v>
+        <v>0.1907003046743014</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1827652992560189</v>
+        <v>0.1892859604015484</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1339178226704476</v>
+        <v>-0.1011509551019856</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.09755297071083646</v>
+        <v>-0.06018431775299149</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.2167169468923618</v>
+        <v>0.222900785917254</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.127729300746239</v>
+        <v>0.1056352926929165</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01507247430370029</v>
+        <v>-0.0169550517878605</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2848181771280878</v>
+        <v>0.251650914339443</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2388036615968048</v>
+        <v>0.2397341173223637</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3198032394167143</v>
+        <v>0.3200505356295054</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.03520185366723183</v>
+        <v>0.001190415786865628</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1542399137872863</v>
+        <v>-0.1457607286982281</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.1457443203572097</v>
+        <v>-0.1326283521132297</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.007477772964499252</v>
+        <v>0.009567348661938979</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.1171894343538114</v>
+        <v>0.1284041624422656</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.1689293856896654</v>
+        <v>0.1845812430466438</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.371150369406557</v>
+        <v>0.3853241765439677</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.00101414312064918</v>
+        <v>0.0110805571198398</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.1345623560764651</v>
+        <v>-0.1165804530565708</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.1218594932675288</v>
+        <v>-0.1040037930102855</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.07069238505890496</v>
+        <v>0.09201966383092497</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.01888250636923061</v>
+        <v>-0.01617100300573071</v>
       </c>
     </row>
     <row r="7">
@@ -1332,79 +1332,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2931</v>
+        <v>2953</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1714199146940913</v>
+        <v>0.1741576647585603</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.02437608821821868</v>
+        <v>-0.02002750728688341</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.2323387278952609</v>
+        <v>0.1907003046743014</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1827652992560189</v>
+        <v>0.1892859604015484</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1339178226704476</v>
+        <v>-0.1011509551019856</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.09755297071083646</v>
+        <v>-0.06018431775299149</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.2167169468923618</v>
+        <v>0.222900785917254</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.127729300746239</v>
+        <v>0.1056352926929165</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.01507247430370029</v>
+        <v>-0.0169550517878605</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2848181771280878</v>
+        <v>0.251650914339443</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2388036615968048</v>
+        <v>0.2397341173223637</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.3198032394167143</v>
+        <v>0.3200505356295054</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.03520185366723183</v>
+        <v>0.001190415786865628</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1542399137872863</v>
+        <v>-0.1457607286982281</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.1457443203572097</v>
+        <v>-0.1326283521132297</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.007477772964499252</v>
+        <v>0.009567348661938979</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.1171894343538114</v>
+        <v>0.1284041624422656</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.1689293856896654</v>
+        <v>0.1845812430466438</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.371150369406557</v>
+        <v>0.3853241765439677</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.00101414312064918</v>
+        <v>0.0110805571198398</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1345623560764651</v>
+        <v>-0.1165804530565708</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.1218594932675288</v>
+        <v>-0.1040037930102855</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0.07069238505890496</v>
+        <v>0.09201966383092497</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.01888250636923061</v>
+        <v>-0.01617100300573071</v>
       </c>
     </row>
     <row r="8">
@@ -1414,79 +1414,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2931</v>
+        <v>2953</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1714199146940913</v>
+        <v>0.1741576647585603</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.02437608821821868</v>
+        <v>-0.02002750728688341</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2323387278952609</v>
+        <v>0.1907003046743014</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1827652992560189</v>
+        <v>0.1892859604015484</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1339178226704476</v>
+        <v>-0.1011509551019856</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.09755297071083646</v>
+        <v>-0.06018431775299149</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.2167169468923618</v>
+        <v>0.222900785917254</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.127729300746239</v>
+        <v>0.1056352926929165</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.01507247430370029</v>
+        <v>-0.0169550517878605</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2848181771280878</v>
+        <v>0.251650914339443</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2388036615968048</v>
+        <v>0.2397341173223637</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.3198032394167143</v>
+        <v>0.3200505356295054</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.03520185366723183</v>
+        <v>0.001190415786865628</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1542399137872863</v>
+        <v>-0.1457607286982281</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.1457443203572097</v>
+        <v>-0.1326283521132297</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.007477772964499252</v>
+        <v>0.009567348661938979</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.1171894343538114</v>
+        <v>0.1284041624422656</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.1689293856896654</v>
+        <v>0.1845812430466438</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.371150369406557</v>
+        <v>0.3853241765439677</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.00101414312064918</v>
+        <v>0.0110805571198398</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1345623560764651</v>
+        <v>-0.1165804530565708</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.1218594932675288</v>
+        <v>-0.1040037930102855</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.07069238505890496</v>
+        <v>0.09201966383092497</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.01888250636923061</v>
+        <v>-0.01617100300573071</v>
       </c>
     </row>
     <row r="9">
@@ -1496,79 +1496,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2931</v>
+        <v>2953</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1714199146940913</v>
+        <v>0.1741576647585603</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.02437608821821868</v>
+        <v>-0.02002750728688341</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.2323387278952609</v>
+        <v>0.1907003046743014</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1827652992560189</v>
+        <v>0.1892859604015484</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.1339178226704476</v>
+        <v>-0.1011509551019856</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.09755297071083646</v>
+        <v>-0.06018431775299149</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2167169468923618</v>
+        <v>0.222900785917254</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.127729300746239</v>
+        <v>0.1056352926929165</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.01507247430370029</v>
+        <v>-0.0169550517878605</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.2848181771280878</v>
+        <v>0.251650914339443</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.2388036615968048</v>
+        <v>0.2397341173223637</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.3198032394167143</v>
+        <v>0.3200505356295054</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.03520185366723183</v>
+        <v>0.001190415786865628</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1542399137872863</v>
+        <v>-0.1457607286982281</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.1457443203572097</v>
+        <v>-0.1326283521132297</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.007477772964499252</v>
+        <v>0.009567348661938979</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.1171894343538114</v>
+        <v>0.1284041624422656</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.1689293856896654</v>
+        <v>0.1845812430466438</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.371150369406557</v>
+        <v>0.3853241765439677</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.00101414312064918</v>
+        <v>0.0110805571198398</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1345623560764651</v>
+        <v>-0.1165804530565708</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.1218594932675288</v>
+        <v>-0.1040037930102855</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.07069238505890496</v>
+        <v>0.09201966383092497</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.01888250636923061</v>
+        <v>-0.01617100300573071</v>
       </c>
     </row>
     <row r="10">
@@ -1578,79 +1578,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2931</v>
+        <v>2953</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1714199146940913</v>
+        <v>0.1741576647585603</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.02437608821821868</v>
+        <v>-0.02002750728688341</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.2323387278952609</v>
+        <v>0.1907003046743014</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1827652992560189</v>
+        <v>0.1892859604015484</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1339178226704476</v>
+        <v>-0.1011509551019856</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.09755297071083646</v>
+        <v>-0.06018431775299149</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2167169468923618</v>
+        <v>0.222900785917254</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.127729300746239</v>
+        <v>0.1056352926929165</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.01507247430370029</v>
+        <v>-0.0169550517878605</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2848181771280878</v>
+        <v>0.251650914339443</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2388036615968048</v>
+        <v>0.2397341173223637</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3198032394167143</v>
+        <v>0.3200505356295054</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.03520185366723183</v>
+        <v>0.001190415786865628</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1542399137872863</v>
+        <v>-0.1457607286982281</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.1457443203572097</v>
+        <v>-0.1326283521132297</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.007477772964499252</v>
+        <v>0.009567348661938979</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.1171894343538114</v>
+        <v>0.1284041624422656</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.1689293856896654</v>
+        <v>0.1845812430466438</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.371150369406557</v>
+        <v>0.3853241765439677</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.00101414312064918</v>
+        <v>0.0110805571198398</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.1345623560764651</v>
+        <v>-0.1165804530565708</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.1218594932675288</v>
+        <v>-0.1040037930102855</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.07069238505890496</v>
+        <v>0.09201966383092497</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.01888250636923061</v>
+        <v>-0.01617100300573071</v>
       </c>
     </row>
     <row r="11">
@@ -1660,79 +1660,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2438</v>
+        <v>2457</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.361824710173309</v>
+        <v>-0.3089969787168982</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2673924529390774</v>
+        <v>-0.2907575832240923</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.3955702475035707</v>
+        <v>0.3774843084039858</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.2355563639532932</v>
+        <v>0.293143911284993</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1996375548019671</v>
+        <v>-0.1622001503626009</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1350703895124283</v>
+        <v>-0.126724034243054</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.235371787470342</v>
+        <v>0.171311362431112</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.06027527289985812</v>
+        <v>-0.1511381827299303</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.004595047488692217</v>
+        <v>-0.04075257990500347</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.6848201758888592</v>
+        <v>0.6454357203214087</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4516226991563599</v>
+        <v>0.4546406518600961</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.5237459747543411</v>
+        <v>0.5665799083733987</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1905853480298205</v>
+        <v>-0.1426326958927859</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2890150012548176</v>
+        <v>-0.2691629033705283</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.4321820511491623</v>
+        <v>-0.3999290183500648</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.05889500570351203</v>
+        <v>-0.01760507345566253</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.07710631903165677</v>
+        <v>0.1055628892499314</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.1605050584642456</v>
+        <v>0.1999116756862946</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.4418896634233818</v>
+        <v>0.4791899106020523</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.1496340472968427</v>
+        <v>-0.1192317744202569</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.2415452296012575</v>
+        <v>-0.1988713977522067</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.2929622079947904</v>
+        <v>-0.2499643825501465</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.07603930053898722</v>
+        <v>-0.02292425796864705</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.2915050255686822</v>
+        <v>-0.2423711614781539</v>
       </c>
     </row>
     <row r="12">
@@ -1742,79 +1742,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2438</v>
+        <v>2457</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.361824710173309</v>
+        <v>-0.3089969787168982</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2673924529390774</v>
+        <v>-0.2907575832240923</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.3955702475035707</v>
+        <v>0.3774843084039858</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2355563639532932</v>
+        <v>0.293143911284993</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.1996375548019671</v>
+        <v>-0.1622001503626009</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1350703895124283</v>
+        <v>-0.126724034243054</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.235371787470342</v>
+        <v>0.171311362431112</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.06027527289985812</v>
+        <v>-0.1511381827299303</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.004595047488692217</v>
+        <v>-0.04075257990500347</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.6848201758888592</v>
+        <v>0.6454357203214087</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4516226991563599</v>
+        <v>0.4546406518600961</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.5237459747543411</v>
+        <v>0.5665799083733987</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1905853480298205</v>
+        <v>-0.1426326958927859</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2890150012548176</v>
+        <v>-0.2691629033705283</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.4321820511491623</v>
+        <v>-0.3999290183500648</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.05889500570351203</v>
+        <v>-0.01760507345566253</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.07710631903165677</v>
+        <v>0.1055628892499314</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.1605050584642456</v>
+        <v>0.1999116756862946</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.4418896634233818</v>
+        <v>0.4791899106020523</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.1496340472968427</v>
+        <v>-0.1192317744202569</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.2415452296012575</v>
+        <v>-0.1988713977522067</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.2929622079947904</v>
+        <v>-0.2499643825501465</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.07603930053898722</v>
+        <v>-0.02292425796864705</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.2915050255686822</v>
+        <v>-0.2423711614781539</v>
       </c>
     </row>
     <row r="13">
@@ -1824,79 +1824,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2438</v>
+        <v>2457</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.361824710173309</v>
+        <v>-0.3089969787168982</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.2673924529390774</v>
+        <v>-0.2907575832240923</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.3955702475035707</v>
+        <v>0.3774843084039858</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.2355563639532932</v>
+        <v>0.293143911284993</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.1996375548019671</v>
+        <v>-0.1622001503626009</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1350703895124283</v>
+        <v>-0.126724034243054</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.235371787470342</v>
+        <v>0.171311362431112</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.06027527289985812</v>
+        <v>-0.1511381827299303</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.004595047488692217</v>
+        <v>-0.04075257990500347</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.6848201758888592</v>
+        <v>0.6454357203214087</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.4516226991563599</v>
+        <v>0.4546406518600961</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.5237459747543411</v>
+        <v>0.5665799083733987</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1905853480298205</v>
+        <v>-0.1426326958927859</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2890150012548176</v>
+        <v>-0.2691629033705283</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.4321820511491623</v>
+        <v>-0.3999290183500648</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.05889500570351203</v>
+        <v>-0.01760507345566253</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.07710631903165677</v>
+        <v>0.1055628892499314</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.1605050584642456</v>
+        <v>0.1999116756862946</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.4418896634233818</v>
+        <v>0.4791899106020523</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.1496340472968427</v>
+        <v>-0.1192317744202569</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2415452296012575</v>
+        <v>-0.1988713977522067</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.2929622079947904</v>
+        <v>-0.2499643825501465</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.07603930053898722</v>
+        <v>-0.02292425796864705</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.2915050255686822</v>
+        <v>-0.2423711614781539</v>
       </c>
     </row>
     <row r="14">
@@ -1906,79 +1906,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2438</v>
+        <v>2457</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.361824710173309</v>
+        <v>-0.3089969787168982</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2673924529390774</v>
+        <v>-0.2907575832240923</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.3955702475035707</v>
+        <v>0.3774843084039858</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.2355563639532932</v>
+        <v>0.293143911284993</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.1996375548019671</v>
+        <v>-0.1622001503626009</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1350703895124283</v>
+        <v>-0.126724034243054</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.235371787470342</v>
+        <v>0.171311362431112</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.06027527289985812</v>
+        <v>-0.1511381827299303</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.004595047488692217</v>
+        <v>-0.04075257990500347</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.6848201758888592</v>
+        <v>0.6454357203214087</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4516226991563599</v>
+        <v>0.4546406518600961</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.5237459747543411</v>
+        <v>0.5665799083733987</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.1905853480298205</v>
+        <v>-0.1426326958927859</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2890150012548176</v>
+        <v>-0.2691629033705283</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.4321820511491623</v>
+        <v>-0.3999290183500648</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.05889500570351203</v>
+        <v>-0.01760507345566253</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.07710631903165677</v>
+        <v>0.1055628892499314</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.1605050584642456</v>
+        <v>0.1999116756862946</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.4418896634233818</v>
+        <v>0.4791899106020523</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.1496340472968427</v>
+        <v>-0.1192317744202569</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.2415452296012575</v>
+        <v>-0.1988713977522067</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.2929622079947904</v>
+        <v>-0.2499643825501465</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.07603930053898722</v>
+        <v>-0.02292425796864705</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.2915050255686822</v>
+        <v>-0.2423711614781539</v>
       </c>
     </row>
     <row r="15">
@@ -1988,79 +1988,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2438</v>
+        <v>2457</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.361824710173309</v>
+        <v>-0.3089969787168982</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2673924529390774</v>
+        <v>-0.2907575832240923</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.3955702475035707</v>
+        <v>0.3774843084039858</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2355563639532932</v>
+        <v>0.293143911284993</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.1996375548019671</v>
+        <v>-0.1622001503626009</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1350703895124283</v>
+        <v>-0.126724034243054</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.235371787470342</v>
+        <v>0.171311362431112</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.06027527289985812</v>
+        <v>-0.1511381827299303</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.004595047488692217</v>
+        <v>-0.04075257990500347</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.6848201758888592</v>
+        <v>0.6454357203214087</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.4516226991563599</v>
+        <v>0.4546406518600961</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.5237459747543411</v>
+        <v>0.5665799083733987</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.1905853480298205</v>
+        <v>-0.1426326958927859</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.2890150012548176</v>
+        <v>-0.2691629033705283</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.4321820511491623</v>
+        <v>-0.3999290183500648</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.05889500570351203</v>
+        <v>-0.01760507345566253</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.07710631903165677</v>
+        <v>0.1055628892499314</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.1605050584642456</v>
+        <v>0.1999116756862946</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.4418896634233818</v>
+        <v>0.4791899106020523</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.1496340472968427</v>
+        <v>-0.1192317744202569</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.2415452296012575</v>
+        <v>-0.1988713977522067</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.2929622079947904</v>
+        <v>-0.2499643825501465</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.07603930053898722</v>
+        <v>-0.02292425796864705</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.2915050255686822</v>
+        <v>-0.2423711614781539</v>
       </c>
     </row>
     <row r="16">
@@ -2070,79 +2070,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1945</v>
+        <v>1961</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.552536751002151</v>
+        <v>-0.5299685002624983</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.008032880863773073</v>
+        <v>-0.03980002784689418</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2838532067907025</v>
+        <v>0.3039593591292302</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.9286177436708698</v>
+        <v>1.007372163883296</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.07179440576802421</v>
+        <v>0.02187487571094238</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.115171780329355</v>
+        <v>0.02667866426480003</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.1612190064594614</v>
+        <v>0.0936656175493269</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.08772973294473729</v>
+        <v>-0.2332522880468204</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.3412896146109077</v>
+        <v>0.3295096188790225</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.133978333775666</v>
+        <v>1.136838437302885</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.5674595887568756</v>
+        <v>0.6258718349748449</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.4423987098990523</v>
+        <v>0.5017289048937954</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3733863077767481</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.5944651842233384</v>
+        <v>-0.5565192252095983</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.4023719490464188</v>
+        <v>-0.3447573217192996</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.1713286713286664</v>
+        <v>0.246672459876919</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.5297876378099104</v>
+        <v>0.5800731552162759</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.1991427254386622</v>
+        <v>0.2739174902219688</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.6717076176566295</v>
+        <v>0.7429622020927908</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.0885328937437535</v>
+        <v>0.1428846960316079</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.007999046106263563</v>
+        <v>0.08460516410097796</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.1169791056697704</v>
+        <v>0.1416232169963223</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.09156720504722671</v>
+        <v>0.007889021849941003</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.06887718328808745</v>
+        <v>0.13092355143921</v>
       </c>
     </row>
     <row r="17">
@@ -2152,79 +2152,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1945</v>
+        <v>1961</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.552536751002151</v>
+        <v>-0.5299685002624983</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.008032880863773073</v>
+        <v>-0.03980002784689418</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2838532067907025</v>
+        <v>0.3039593591292302</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.9286177436708698</v>
+        <v>1.007372163883296</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.07179440576802421</v>
+        <v>0.02187487571094238</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.115171780329355</v>
+        <v>0.02667866426480003</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.1612190064594614</v>
+        <v>0.0936656175493269</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.08772973294473729</v>
+        <v>-0.2332522880468204</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.3412896146109077</v>
+        <v>0.3295096188790225</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.133978333775666</v>
+        <v>1.136838437302885</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.5674595887568756</v>
+        <v>0.6258718349748449</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.4423987098990523</v>
+        <v>0.5017289048937954</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.3733863077767481</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.5944651842233384</v>
+        <v>-0.5565192252095983</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.4023719490464188</v>
+        <v>-0.3447573217192996</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.1713286713286664</v>
+        <v>0.246672459876919</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.5297876378099104</v>
+        <v>0.5800731552162759</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.1991427254386622</v>
+        <v>0.2739174902219688</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.6717076176566295</v>
+        <v>0.7429622020927908</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.0885328937437535</v>
+        <v>0.1428846960316079</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.007999046106263563</v>
+        <v>0.08460516410097796</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.1169791056697704</v>
+        <v>0.1416232169963223</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.09156720504722671</v>
+        <v>0.007889021849941003</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.06887718328808745</v>
+        <v>0.13092355143921</v>
       </c>
     </row>
     <row r="18">
@@ -2234,79 +2234,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1945</v>
+        <v>1961</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.552536751002151</v>
+        <v>-0.5299685002624983</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.008032880863773073</v>
+        <v>-0.03980002784689418</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.2838532067907025</v>
+        <v>0.3039593591292302</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.9286177436708698</v>
+        <v>1.007372163883296</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.07179440576802421</v>
+        <v>0.02187487571094238</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.115171780329355</v>
+        <v>0.02667866426480003</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.1612190064594614</v>
+        <v>0.0936656175493269</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.08772973294473729</v>
+        <v>-0.2332522880468204</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.3412896146109077</v>
+        <v>0.3295096188790225</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.133978333775666</v>
+        <v>1.136838437302885</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.5674595887568756</v>
+        <v>0.6258718349748449</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.4423987098990523</v>
+        <v>0.5017289048937954</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.3733863077767481</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.5944651842233384</v>
+        <v>-0.5565192252095983</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.4023719490464188</v>
+        <v>-0.3447573217192996</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.1713286713286664</v>
+        <v>0.246672459876919</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.5297876378099104</v>
+        <v>0.5800731552162759</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.1991427254386622</v>
+        <v>0.2739174902219688</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.6717076176566295</v>
+        <v>0.7429622020927908</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.0885328937437535</v>
+        <v>0.1428846960316079</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.007999046106263563</v>
+        <v>0.08460516410097796</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.1169791056697704</v>
+        <v>0.1416232169963223</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.09156720504722671</v>
+        <v>0.007889021849941003</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.06887718328808745</v>
+        <v>0.13092355143921</v>
       </c>
     </row>
     <row r="19">
@@ -2316,79 +2316,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1945</v>
+        <v>1961</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.552536751002151</v>
+        <v>-0.5299685002624983</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.008032880863773073</v>
+        <v>-0.03980002784689418</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2838532067907025</v>
+        <v>0.3039593591292302</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.9286177436708698</v>
+        <v>1.007372163883296</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.07179440576802421</v>
+        <v>0.02187487571094238</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.115171780329355</v>
+        <v>0.02667866426480003</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.1612190064594614</v>
+        <v>0.0936656175493269</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.08772973294473729</v>
+        <v>-0.2332522880468204</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.3412896146109077</v>
+        <v>0.3295096188790225</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.133978333775666</v>
+        <v>1.136838437302885</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.5674595887568756</v>
+        <v>0.6258718349748449</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.4423987098990523</v>
+        <v>0.5017289048937954</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.3733863077767481</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.5944651842233384</v>
+        <v>-0.5565192252095983</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.4023719490464188</v>
+        <v>-0.3447573217192996</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.1713286713286664</v>
+        <v>0.246672459876919</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.5297876378099104</v>
+        <v>0.5800731552162759</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.1991427254386622</v>
+        <v>0.2739174902219688</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.6717076176566295</v>
+        <v>0.7429622020927908</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.0885328937437535</v>
+        <v>0.1428846960316079</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.007999046106263563</v>
+        <v>0.08460516410097796</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.1169791056697704</v>
+        <v>0.1416232169963223</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.09156720504722671</v>
+        <v>0.007889021849941003</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.06887718328808745</v>
+        <v>0.13092355143921</v>
       </c>
     </row>
     <row r="20">
@@ -2398,79 +2398,79 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1945</v>
+        <v>1961</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.552536751002151</v>
+        <v>-0.5299685002624983</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.008032880863773073</v>
+        <v>-0.03980002784689418</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.2838532067907025</v>
+        <v>0.3039593591292302</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.9286177436708698</v>
+        <v>1.007372163883296</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.07179440576802421</v>
+        <v>0.02187487571094238</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.115171780329355</v>
+        <v>0.02667866426480003</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.1612190064594614</v>
+        <v>0.0936656175493269</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.08772973294473729</v>
+        <v>-0.2332522880468204</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.3412896146109077</v>
+        <v>0.3295096188790225</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.133978333775666</v>
+        <v>1.136838437302885</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.5674595887568756</v>
+        <v>0.6258718349748449</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.4423987098990523</v>
+        <v>0.5017289048937954</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.3733863077767481</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.5944651842233384</v>
+        <v>-0.5565192252095983</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.4023719490464188</v>
+        <v>-0.3447573217192996</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.1713286713286664</v>
+        <v>0.246672459876919</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.5297876378099104</v>
+        <v>0.5800731552162759</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.1991427254386622</v>
+        <v>0.2739174902219688</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.6717076176566295</v>
+        <v>0.7429622020927908</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.0885328937437535</v>
+        <v>0.1428846960316079</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.007999046106263563</v>
+        <v>0.08460516410097796</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.1169791056697704</v>
+        <v>0.1416232169963223</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.09156720504722671</v>
+        <v>0.007889021849941003</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.06887718328808745</v>
+        <v>0.13092355143921</v>
       </c>
     </row>
     <row r="21">
@@ -2480,79 +2480,79 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1458</v>
+        <v>1470</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.9519430970943219</v>
+        <v>-0.9430318597783867</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.1796894397168529</v>
+        <v>0.1303853551044583</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.8235758530931605</v>
+        <v>0.8729319015691317</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.405782024516128</v>
+        <v>1.565181494512103</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.08883598722677277</v>
+        <v>-0.0626416895358517</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.3026291763757101</v>
+        <v>0.2295184208570973</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.007844773330624832</v>
+        <v>-0.1598840781910411</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.3824677178844524</v>
+        <v>0.2499380036592385</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.8046429879310608</v>
+        <v>0.822758040532193</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.232607596868178</v>
+        <v>1.285208636088669</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.5503830860246381</v>
+        <v>0.6089341655981499</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.3399396935055989</v>
+        <v>0.4001028886336258</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.3733863077767481</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.5944651842233384</v>
+        <v>-0.5565192252095983</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.1187660515852826</v>
+        <v>-0.04658321161442558</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.3114247813290234</v>
+        <v>0.4194191950809483</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.4237644011968769</v>
+        <v>0.4916624236252503</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.1820311580190932</v>
+        <v>0.2230009932769548</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.9454926963698327</v>
+        <v>0.9805725211695133</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.5847683489114459</v>
+        <v>0.584161002888365</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.1791147203020174</v>
+        <v>0.2882711518810268</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.0610960503482616</v>
+        <v>-0.01809100701751021</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.1173286372527897</v>
+        <v>0.2659533591464012</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.1510759201569201</v>
+        <v>0.2123064360566005</v>
       </c>
     </row>
     <row r="22">
@@ -2562,79 +2562,79 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1458</v>
+        <v>1470</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.9519430970943219</v>
+        <v>-0.9430318597783867</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.1796894397168529</v>
+        <v>0.1303853551044583</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.8235758530931605</v>
+        <v>0.8729319015691317</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.405782024516128</v>
+        <v>1.565181494512103</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.08883598722677277</v>
+        <v>-0.0626416895358517</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.3026291763757101</v>
+        <v>0.2295184208570973</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.007844773330624832</v>
+        <v>-0.1598840781910411</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.3824677178844524</v>
+        <v>0.2499380036592385</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.8046429879310608</v>
+        <v>0.822758040532193</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.232607596868178</v>
+        <v>1.285208636088669</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.5503830860246381</v>
+        <v>0.6089341655981499</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.3399396935055989</v>
+        <v>0.4001028886336258</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.3733863077767481</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.5944651842233384</v>
+        <v>-0.5565192252095983</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.1187660515852826</v>
+        <v>-0.04658321161442558</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.3114247813290234</v>
+        <v>0.4194191950809483</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.4237644011968769</v>
+        <v>0.4916624236252503</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.1820311580190932</v>
+        <v>0.2230009932769548</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.9454926963698327</v>
+        <v>0.9805725211695133</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.5847683489114459</v>
+        <v>0.584161002888365</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.1791147203020174</v>
+        <v>0.2882711518810268</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.0610960503482616</v>
+        <v>-0.01809100701751021</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.1173286372527897</v>
+        <v>0.2659533591464012</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.1510759201569201</v>
+        <v>0.2123064360566005</v>
       </c>
     </row>
     <row r="23">
@@ -2644,79 +2644,79 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1458</v>
+        <v>1470</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.9519430970943219</v>
+        <v>-0.9430318597783867</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1796894397168529</v>
+        <v>0.1303853551044583</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.8235758530931605</v>
+        <v>0.8729319015691317</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.405782024516128</v>
+        <v>1.565181494512103</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.08883598722677277</v>
+        <v>-0.0626416895358517</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.3026291763757101</v>
+        <v>0.2295184208570973</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.007844773330624832</v>
+        <v>-0.1598840781910411</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.3824677178844524</v>
+        <v>0.2499380036592385</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.8046429879310608</v>
+        <v>0.822758040532193</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.232607596868178</v>
+        <v>1.285208636088669</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.5503830860246381</v>
+        <v>0.6089341655981499</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.3399396935055989</v>
+        <v>0.4001028886336258</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.3733863077767481</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.5944651842233384</v>
+        <v>-0.5565192252095983</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.1187660515852826</v>
+        <v>-0.04658321161442558</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.3114247813290234</v>
+        <v>0.4194191950809483</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.4237644011968769</v>
+        <v>0.4916624236252503</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.1820311580190932</v>
+        <v>0.2230009932769548</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.9454926963698327</v>
+        <v>0.9805725211695133</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.5847683489114459</v>
+        <v>0.584161002888365</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.1791147203020174</v>
+        <v>0.2882711518810268</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.0610960503482616</v>
+        <v>-0.01809100701751021</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.1173286372527897</v>
+        <v>0.2659533591464012</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.1510759201569201</v>
+        <v>0.2123064360566005</v>
       </c>
     </row>
     <row r="24">
@@ -2726,79 +2726,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1458</v>
+        <v>1470</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.9519430970943219</v>
+        <v>-0.9430318597783867</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.1796894397168529</v>
+        <v>0.1303853551044583</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.8235758530931605</v>
+        <v>0.8729319015691317</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.405782024516128</v>
+        <v>1.565181494512103</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.08883598722677277</v>
+        <v>-0.0626416895358517</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.3026291763757101</v>
+        <v>0.2295184208570973</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.007844773330624832</v>
+        <v>-0.1598840781910411</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.3824677178844524</v>
+        <v>0.2499380036592385</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.8046429879310608</v>
+        <v>0.822758040532193</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.232607596868178</v>
+        <v>1.285208636088669</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.5503830860246381</v>
+        <v>0.6089341655981499</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.3399396935055989</v>
+        <v>0.4001028886336258</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.3733863077767481</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.5944651842233384</v>
+        <v>-0.5565192252095983</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.1187660515852826</v>
+        <v>-0.04658321161442558</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.3114247813290234</v>
+        <v>0.4194191950809483</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.4237644011968769</v>
+        <v>0.4916624236252503</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.1820311580190932</v>
+        <v>0.2230009932769548</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.9454926963698327</v>
+        <v>0.9805725211695133</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.5847683489114459</v>
+        <v>0.584161002888365</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.1791147203020174</v>
+        <v>0.2882711518810268</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.0610960503482616</v>
+        <v>-0.01809100701751021</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.1173286372527897</v>
+        <v>0.2659533591464012</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.1510759201569201</v>
+        <v>0.2123064360566005</v>
       </c>
     </row>
     <row r="25">
@@ -2808,79 +2808,79 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1458</v>
+        <v>1470</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.9519430970943219</v>
+        <v>-0.9430318597783867</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.1796894397168529</v>
+        <v>0.1303853551044583</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.8235758530931605</v>
+        <v>0.8729319015691317</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.405782024516128</v>
+        <v>1.565181494512103</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.08883598722677277</v>
+        <v>-0.0626416895358517</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.3026291763757101</v>
+        <v>0.2295184208570973</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.007844773330624832</v>
+        <v>-0.1598840781910411</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.3824677178844524</v>
+        <v>0.2499380036592385</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.8046429879310608</v>
+        <v>0.822758040532193</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.232607596868178</v>
+        <v>1.285208636088669</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.5503830860246381</v>
+        <v>0.6089341655981499</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.3399396935055989</v>
+        <v>0.4001028886336258</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.3733863077767481</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.5944651842233384</v>
+        <v>-0.5565192252095983</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.1187660515852826</v>
+        <v>-0.04658321161442558</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.3114247813290234</v>
+        <v>0.4194191950809483</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.4237644011968769</v>
+        <v>0.4916624236252503</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.1820311580190932</v>
+        <v>0.2230009932769548</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.9454926963698327</v>
+        <v>0.9805725211695133</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.5847683489114459</v>
+        <v>0.584161002888365</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.1791147203020174</v>
+        <v>0.2882711518810268</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.0610960503482616</v>
+        <v>-0.01809100701751021</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.1173286372527897</v>
+        <v>0.2659533591464012</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>0.1510759201569201</v>
+        <v>0.2123064360566005</v>
       </c>
     </row>
     <row r="26">
@@ -2890,79 +2890,79 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.9046074320225728</v>
+        <v>0.8646681047161522</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.136850525846029</v>
+        <v>1.181040472696694</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.232573808103382</v>
+        <v>1.4476445452473</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.95111263119643</v>
+        <v>2.072280885992825</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2251686388968537</v>
+        <v>-0.2316748200294256</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.1662965247056292</v>
+        <v>0.1280985425609487</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.9280901721036301</v>
+        <v>0.7528948264742823</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.220989740782173</v>
+        <v>1.115286292951268</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.7077090652543916</v>
+        <v>0.7939972586792763</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.9593835531523283</v>
+        <v>1.014205926061564</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.516230080560149</v>
+        <v>0.5750588268447672</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.7497757590793697</v>
+        <v>0.806606953674283</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.4758453241701872</v>
+        <v>-0.4099111800366586</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.1846291186495677</v>
+        <v>-0.1500151601689481</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.6538648263087623</v>
+        <v>0.753527138920937</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.7972434820484082</v>
+        <v>0.9689304796136682</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.663326345070935</v>
+        <v>0.7632170739986393</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>0.353146832214847</v>
+        <v>0.3248339871669756</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1.185054640243898</v>
+        <v>1.150294177652867</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.8585534276246563</v>
+        <v>0.8557156532617611</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.4186766641760755</v>
+        <v>0.4919371396610615</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>0.4047700043617795</v>
+        <v>0.4778121308631</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>0.4326694902526285</v>
+        <v>0.5785270629991146</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.2604467135879389</v>
+        <v>-0.0938160129229999</v>
       </c>
     </row>
     <row r="27">
@@ -2972,79 +2972,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.9046074320225728</v>
+        <v>0.8646681047161522</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.136850525846029</v>
+        <v>1.181040472696694</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.232573808103382</v>
+        <v>1.4476445452473</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.95111263119643</v>
+        <v>2.072280885992825</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.2251686388968537</v>
+        <v>-0.2316748200294256</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.1662965247056292</v>
+        <v>0.1280985425609487</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.9280901721036301</v>
+        <v>0.7528948264742823</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.220989740782173</v>
+        <v>1.115286292951268</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.7077090652543916</v>
+        <v>0.7939972586792763</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.9593835531523283</v>
+        <v>1.014205926061564</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.516230080560149</v>
+        <v>0.5750588268447672</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.7497757590793697</v>
+        <v>0.806606953674283</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.4758453241701872</v>
+        <v>-0.4099111800366586</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.1846291186495677</v>
+        <v>-0.1500151601689481</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.6538648263087623</v>
+        <v>0.753527138920937</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.7972434820484082</v>
+        <v>0.9689304796136682</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.663326345070935</v>
+        <v>0.7632170739986393</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>0.353146832214847</v>
+        <v>0.3248339871669756</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1.185054640243898</v>
+        <v>1.150294177652867</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.8585534276246563</v>
+        <v>0.8557156532617611</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.4186766641760755</v>
+        <v>0.4919371396610615</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>0.4047700043617795</v>
+        <v>0.4778121308631</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>0.4326694902526285</v>
+        <v>0.5785270629991146</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.2604467135879389</v>
+        <v>-0.0938160129229999</v>
       </c>
     </row>
     <row r="28">
@@ -3054,79 +3054,79 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.9046074320225728</v>
+        <v>0.8646681047161522</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.136850525846029</v>
+        <v>1.181040472696694</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.232573808103382</v>
+        <v>1.4476445452473</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.95111263119643</v>
+        <v>2.072280885992825</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2251686388968537</v>
+        <v>-0.2316748200294256</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1662965247056292</v>
+        <v>0.1280985425609487</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.9280901721036301</v>
+        <v>0.7528948264742823</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.220989740782173</v>
+        <v>1.115286292951268</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.7077090652543916</v>
+        <v>0.7939972586792763</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.9593835531523283</v>
+        <v>1.014205926061564</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.516230080560149</v>
+        <v>0.5750588268447672</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.7497757590793697</v>
+        <v>0.806606953674283</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.4758453241701872</v>
+        <v>-0.4099111800366586</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.1846291186495677</v>
+        <v>-0.1500151601689481</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.6538648263087623</v>
+        <v>0.753527138920937</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.7972434820484082</v>
+        <v>0.9689304796136682</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.663326345070935</v>
+        <v>0.7632170739986393</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>0.353146832214847</v>
+        <v>0.3248339871669756</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>1.185054640243898</v>
+        <v>1.150294177652867</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.8585534276246563</v>
+        <v>0.8557156532617611</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.4186766641760755</v>
+        <v>0.4919371396610615</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>0.4047700043617795</v>
+        <v>0.4778121308631</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.4326694902526285</v>
+        <v>0.5785270629991146</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.2604467135879389</v>
+        <v>-0.0938160129229999</v>
       </c>
     </row>
     <row r="29">
@@ -3136,79 +3136,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.9046074320225728</v>
+        <v>0.8646681047161522</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.136850525846029</v>
+        <v>1.181040472696694</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.232573808103382</v>
+        <v>1.4476445452473</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.95111263119643</v>
+        <v>2.072280885992825</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2251686388968537</v>
+        <v>-0.2316748200294256</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1662965247056292</v>
+        <v>0.1280985425609487</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.9280901721036301</v>
+        <v>0.7528948264742823</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.220989740782173</v>
+        <v>1.115286292951268</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.7077090652543916</v>
+        <v>0.7939972586792763</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.9593835531523283</v>
+        <v>1.014205926061564</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.516230080560149</v>
+        <v>0.5750588268447672</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.7497757590793697</v>
+        <v>0.806606953674283</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.4758453241701872</v>
+        <v>-0.4099111800366586</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.1846291186495677</v>
+        <v>-0.1500151601689481</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.6538648263087623</v>
+        <v>0.753527138920937</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.7972434820484082</v>
+        <v>0.9689304796136682</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.663326345070935</v>
+        <v>0.7632170739986393</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.353146832214847</v>
+        <v>0.3248339871669756</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1.185054640243898</v>
+        <v>1.150294177652867</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.8585534276246563</v>
+        <v>0.8557156532617611</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.4186766641760755</v>
+        <v>0.4919371396610615</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>0.4047700043617795</v>
+        <v>0.4778121308631</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.4326694902526285</v>
+        <v>0.5785270629991146</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.2604467135879389</v>
+        <v>-0.0938160129229999</v>
       </c>
     </row>
     <row r="30">
@@ -3218,79 +3218,79 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.9046074320225728</v>
+        <v>0.8646681047161522</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.136850525846029</v>
+        <v>1.181040472696694</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.232573808103382</v>
+        <v>1.4476445452473</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.95111263119643</v>
+        <v>2.072280885992825</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.2251686388968537</v>
+        <v>-0.2316748200294256</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.1662965247056292</v>
+        <v>0.1280985425609487</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.9280901721036301</v>
+        <v>0.7528948264742823</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.220989740782173</v>
+        <v>1.115286292951268</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.7077090652543916</v>
+        <v>0.7939972586792763</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.9593835531523283</v>
+        <v>1.014205926061564</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.516230080560149</v>
+        <v>0.5750588268447672</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.7497757590793697</v>
+        <v>0.806606953674283</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.4758453241701872</v>
+        <v>-0.4099111800366586</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.1846291186495677</v>
+        <v>-0.1500151601689481</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.6538648263087623</v>
+        <v>0.753527138920937</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.7972434820484082</v>
+        <v>0.9689304796136682</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.663326345070935</v>
+        <v>0.7632170739986393</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.353146832214847</v>
+        <v>0.3248339871669756</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.185054640243898</v>
+        <v>1.150294177652867</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.8585534276246563</v>
+        <v>0.8557156532617611</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.4186766641760755</v>
+        <v>0.4919371396610615</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>0.4047700043617795</v>
+        <v>0.4778121308631</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>0.4326694902526285</v>
+        <v>0.5785270629991146</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.2604467135879389</v>
+        <v>-0.0938160129229999</v>
       </c>
     </row>
     <row r="31">
@@ -3300,79 +3300,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.164878857938177</v>
+        <v>1.021267795215977</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.8301020595883628</v>
+        <v>0.9782007161043893</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.437072785608493</v>
+        <v>1.549064423543449</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.95111263119643</v>
+        <v>1.970861007696683</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.2251686388968537</v>
+        <v>-0.3330946983255743</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.5752944797158577</v>
+        <v>0.4323581774493874</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.461832503391975</v>
+        <v>2.274193000916469</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.280975981700351</v>
+        <v>1.27582444655615</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.3168810986800281</v>
+        <v>-0.222262903922342</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.7544655203654429</v>
+        <v>0.8109538935412459</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.6186890969535952</v>
+        <v>0.6766848431049226</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1350216607187136</v>
+        <v>0.1968508561133078</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.3733863077767481</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.2252069469242102</v>
+        <v>0.256488904871695</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>0.9215423917275984</v>
+        <v>1.120457418024145</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.8999128865658577</v>
+        <v>1.070763473503689</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.7659957495883845</v>
+        <v>0.7632170739986393</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.6611550457672024</v>
+        <v>0.6303329688370383</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>1.698401662831159</v>
+        <v>1.659459147102972</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>0.8585534276246563</v>
+        <v>0.8557156532617611</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>1.137362495798257</v>
+        <v>1.306601090781221</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>0.3639560946429938</v>
+        <v>0.334892577720737</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.3903757772370966</v>
+        <v>-0.03371783496006486</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.2604467135879389</v>
+        <v>0.00822480340353593</v>
       </c>
     </row>
     <row r="32">
@@ -3382,79 +3382,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.164878857938177</v>
+        <v>1.021267795215977</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.8301020595883628</v>
+        <v>0.9782007161043893</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.437072785608493</v>
+        <v>1.549064423543449</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.95111263119643</v>
+        <v>1.970861007696683</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2251686388968537</v>
+        <v>-0.3330946983255743</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.5752944797158577</v>
+        <v>0.4323581774493874</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.461832503391975</v>
+        <v>2.274193000916469</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.280975981700351</v>
+        <v>1.27582444655615</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.3168810986800281</v>
+        <v>-0.222262903922342</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.7544655203654429</v>
+        <v>0.8109538935412459</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.6186890969535952</v>
+        <v>0.6766848431049226</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1350216607187136</v>
+        <v>0.1968508561133078</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.3733863077767481</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.2252069469242102</v>
+        <v>0.256488904871695</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0.9215423917275984</v>
+        <v>1.120457418024145</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0.8999128865658577</v>
+        <v>1.070763473503689</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.7659957495883845</v>
+        <v>0.7632170739986393</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.6611550457672024</v>
+        <v>0.6303329688370383</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>1.698401662831159</v>
+        <v>1.659459147102972</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.8585534276246563</v>
+        <v>0.8557156532617611</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>1.137362495798257</v>
+        <v>1.306601090781221</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>0.3639560946429938</v>
+        <v>0.334892577720737</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.3903757772370966</v>
+        <v>-0.03371783496006486</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.2604467135879389</v>
+        <v>0.00822480340353593</v>
       </c>
     </row>
     <row r="33">
@@ -3464,79 +3464,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.164878857938177</v>
+        <v>1.021267795215977</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.8301020595883628</v>
+        <v>0.9782007161043893</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.437072785608493</v>
+        <v>1.549064423543449</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.95111263119643</v>
+        <v>1.970861007696683</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2251686388968537</v>
+        <v>-0.3330946983255743</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.5752944797158577</v>
+        <v>0.4323581774493874</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.461832503391975</v>
+        <v>2.274193000916469</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.280975981700351</v>
+        <v>1.27582444655615</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.3168810986800281</v>
+        <v>-0.222262903922342</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.7544655203654429</v>
+        <v>0.8109538935412459</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.6186890969535952</v>
+        <v>0.6766848431049226</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.1350216607187136</v>
+        <v>0.1968508561133078</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.3733863077767481</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.2252069469242102</v>
+        <v>0.256488904871695</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>0.9215423917275984</v>
+        <v>1.120457418024145</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>0.8999128865658577</v>
+        <v>1.070763473503689</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.7659957495883845</v>
+        <v>0.7632170739986393</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>0.6611550457672024</v>
+        <v>0.6303329688370383</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>1.698401662831159</v>
+        <v>1.659459147102972</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>0.8585534276246563</v>
+        <v>0.8557156532617611</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>1.137362495798257</v>
+        <v>1.306601090781221</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>0.3639560946429938</v>
+        <v>0.334892577720737</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.3903757772370966</v>
+        <v>-0.03371783496006486</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.2604467135879389</v>
+        <v>0.00822480340353593</v>
       </c>
     </row>
     <row r="34">
@@ -3546,79 +3546,79 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.164878857938177</v>
+        <v>1.021267795215977</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.8301020595883628</v>
+        <v>0.9782007161043893</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.437072785608493</v>
+        <v>1.549064423543449</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.95111263119643</v>
+        <v>1.970861007696683</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2251686388968537</v>
+        <v>-0.3330946983255743</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.5752944797158577</v>
+        <v>0.4323581774493874</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.461832503391975</v>
+        <v>2.274193000916469</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.280975981700351</v>
+        <v>1.27582444655615</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3168810986800281</v>
+        <v>-0.222262903922342</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.7544655203654429</v>
+        <v>0.8109538935412459</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.6186890969535952</v>
+        <v>0.6766848431049226</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1350216607187136</v>
+        <v>0.1968508561133078</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3733863077767481</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.2252069469242102</v>
+        <v>0.256488904871695</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>0.9215423917275984</v>
+        <v>1.120457418024145</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0.8999128865658577</v>
+        <v>1.070763473503689</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>0.7659957495883845</v>
+        <v>0.7632170739986393</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>0.6611550457672024</v>
+        <v>0.6303329688370383</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>1.698401662831159</v>
+        <v>1.659459147102972</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>0.8585534276246563</v>
+        <v>0.8557156532617611</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>1.137362495798257</v>
+        <v>1.306601090781221</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>0.3639560946429938</v>
+        <v>0.334892577720737</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.3903757772370966</v>
+        <v>-0.03371783496006486</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.2604467135879389</v>
+        <v>0.00822480340353593</v>
       </c>
     </row>
     <row r="35">
@@ -3880,79 +3880,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.019879371496479</v>
+        <v>-1.037616708070523</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1449787504914539</v>
+        <v>0.1192820674480544</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.381384896296645</v>
+        <v>-1.135412034443526</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.086274399610353</v>
+        <v>-1.12661182844213</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.7956770633262522</v>
+        <v>0.6018380474906024</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.5794174429720158</v>
+        <v>0.357970050282276</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.289794193019993</v>
+        <v>-1.328452876711694</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.7599248296922738</v>
+        <v>-0.6293572558632832</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.08964316030324682</v>
+        <v>0.1009812923750317</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.693373525834261</v>
+        <v>-1.498283054249924</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-1.419313883672338</v>
+        <v>-1.426851252496995</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-1.900083489140535</v>
+        <v>-1.904236419819689</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2090776763265865</v>
+        <v>-0.00708034449938566</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.9179460456167163</v>
+        <v>0.8686987493041514</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.8670901974288725</v>
+        <v>0.7901660978013823</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.04447307078885387</v>
+        <v>-0.05698058760430769</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.6967315155813267</v>
+        <v>-0.7644827297116024</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-1.004001369200076</v>
+        <v>-1.098574078333968</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-2.205114036858745</v>
+        <v>-2.292562555413546</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.006023271084984572</v>
+        <v>-0.0659036757469238</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.800823433526034</v>
+        <v>0.6947818936194139</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0.7249774721169331</v>
+        <v>0.6196193716641289</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.4204261115470516</v>
+        <v>-0.5480364656381482</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.1122609050065435</v>
+        <v>0.09627615297561221</v>
       </c>
     </row>
     <row r="8">
@@ -3962,79 +3962,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.019879371496479</v>
+        <v>-1.037616708070523</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1449787504914539</v>
+        <v>0.1192820674480544</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.381384896296645</v>
+        <v>-1.135412034443526</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.086274399610353</v>
+        <v>-1.12661182844213</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.7956770633262522</v>
+        <v>0.6018380474906024</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.5794174429720158</v>
+        <v>0.357970050282276</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.289794193019993</v>
+        <v>-1.328452876711694</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.7599248296922738</v>
+        <v>-0.6293572558632832</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.08964316030324682</v>
+        <v>0.1009812923750317</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.693373525834261</v>
+        <v>-1.498283054249924</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.419313883672338</v>
+        <v>-1.426851252496995</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.900083489140535</v>
+        <v>-1.904236419819689</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.2090776763265865</v>
+        <v>-0.00708034449938566</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.9179460456167163</v>
+        <v>0.8686987493041514</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.8670901974288725</v>
+        <v>0.7901660978013823</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.04447307078885387</v>
+        <v>-0.05698058760430769</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.6967315155813267</v>
+        <v>-0.7644827297116024</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-1.004001369200076</v>
+        <v>-1.098574078333968</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-2.205114036858745</v>
+        <v>-2.292562555413546</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.006023271084984572</v>
+        <v>-0.0659036757469238</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.800823433526034</v>
+        <v>0.6947818936194139</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.7249774721169331</v>
+        <v>0.6196193716641289</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.4204261115470516</v>
+        <v>-0.5480364656381482</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.1122609050065435</v>
+        <v>0.09627615297561221</v>
       </c>
     </row>
     <row r="9">
@@ -4044,79 +4044,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.019879371496479</v>
+        <v>-1.037616708070523</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1449787504914539</v>
+        <v>0.1192820674480544</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.381384896296645</v>
+        <v>-1.135412034443526</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.086274399610353</v>
+        <v>-1.12661182844213</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.7956770633262522</v>
+        <v>0.6018380474906024</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.5794174429720158</v>
+        <v>0.357970050282276</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.289794193019993</v>
+        <v>-1.328452876711694</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.7599248296922738</v>
+        <v>-0.6293572558632832</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.08964316030324682</v>
+        <v>0.1009812923750317</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.693373525834261</v>
+        <v>-1.498283054249924</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.419313883672338</v>
+        <v>-1.426851252496995</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.900083489140535</v>
+        <v>-1.904236419819689</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2090776763265865</v>
+        <v>-0.00708034449938566</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.9179460456167163</v>
+        <v>0.8686987493041514</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.8670901974288725</v>
+        <v>0.7901660978013823</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.04447307078885387</v>
+        <v>-0.05698058760430769</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.6967315155813267</v>
+        <v>-0.7644827297116024</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-1.004001369200076</v>
+        <v>-1.098574078333968</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-2.205114036858745</v>
+        <v>-2.292562555413546</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.006023271084984572</v>
+        <v>-0.0659036757469238</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.800823433526034</v>
+        <v>0.6947818936194139</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.7249774721169331</v>
+        <v>0.6196193716641289</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.4204261115470516</v>
+        <v>-0.5480364656381482</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.1122609050065435</v>
+        <v>0.09627615297561221</v>
       </c>
     </row>
     <row r="10">
@@ -4126,79 +4126,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.019879371496479</v>
+        <v>-1.037616708070523</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1449787504914539</v>
+        <v>0.1192820674480544</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.381384896296645</v>
+        <v>-1.135412034443526</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.086274399610353</v>
+        <v>-1.12661182844213</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.7956770633262522</v>
+        <v>0.6018380474906024</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.5794174429720158</v>
+        <v>0.357970050282276</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.289794193019993</v>
+        <v>-1.328452876711694</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.7599248296922738</v>
+        <v>-0.6293572558632832</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.08964316030324682</v>
+        <v>0.1009812923750317</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.693373525834261</v>
+        <v>-1.498283054249924</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.419313883672338</v>
+        <v>-1.426851252496995</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.900083489140535</v>
+        <v>-1.904236419819689</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.2090776763265865</v>
+        <v>-0.00708034449938566</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.9179460456167163</v>
+        <v>0.8686987493041514</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.8670901974288725</v>
+        <v>0.7901660978013823</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.04447307078885387</v>
+        <v>-0.05698058760430769</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.6967315155813267</v>
+        <v>-0.7644827297116024</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.004001369200076</v>
+        <v>-1.098574078333968</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-2.205114036858745</v>
+        <v>-2.292562555413546</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.006023271084984572</v>
+        <v>-0.0659036757469238</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.800823433526034</v>
+        <v>0.6947818936194139</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.7249774721169331</v>
+        <v>0.6196193716641289</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.4204261115470516</v>
+        <v>-0.5480364656381482</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.1122609050065435</v>
+        <v>0.09627615297561221</v>
       </c>
     </row>
     <row r="11">
@@ -4208,79 +4208,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.8954432091486808</v>
+        <v>0.7659905063583423</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.6614728624117703</v>
+        <v>0.7204844722576738</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.9781590898450361</v>
+        <v>-0.9350112328403171</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5822421415458408</v>
+        <v>-0.7258102252357119</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.4932577084875405</v>
+        <v>0.4014372458873936</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.3340641016094281</v>
+        <v>0.3139502152260008</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.5827234859492947</v>
+        <v>-0.4248384188803698</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1491660793986469</v>
+        <v>0.3746588083937468</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.01136694070685706</v>
+        <v>0.1009812923750317</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.693373525834261</v>
+        <v>-1.59868466067563</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.116283580642033</v>
+        <v>-1.125646433219885</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.294022883079926</v>
+        <v>-1.402228387691181</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.4713566848138839</v>
+        <v>0.3533563772620383</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.7155168958191354</v>
+        <v>0.6674915058433868</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>1.069519347226439</v>
+        <v>0.9913733412621468</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.1456876456876444</v>
+        <v>0.04362303412608526</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.1906586410873956</v>
+        <v>-0.2614646210596945</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.3967139198073681</v>
+        <v>-0.4949523479516813</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-1.091753712972107</v>
+        <v>-1.185922716379352</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.3700675880968305</v>
+        <v>0.2953778097420496</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.5979836769337439</v>
+        <v>0.493168990393599</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.7249774721169331</v>
+        <v>0.6196193716641289</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.1880931582298189</v>
+        <v>0.05680224403928236</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.720780174783421</v>
+        <v>0.6003084110401389</v>
       </c>
     </row>
     <row r="12">
@@ -4290,79 +4290,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.8954432091486808</v>
+        <v>0.7659905063583423</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.6614728624117703</v>
+        <v>0.7204844722576738</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.9781590898450361</v>
+        <v>-0.9350112328403171</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.5822421415458408</v>
+        <v>-0.7258102252357119</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.4932577084875405</v>
+        <v>0.4014372458873936</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.3340641016094281</v>
+        <v>0.3139502152260008</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.5827234859492947</v>
+        <v>-0.4248384188803698</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.1491660793986469</v>
+        <v>0.3746588083937468</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.01136694070685706</v>
+        <v>0.1009812923750317</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.693373525834261</v>
+        <v>-1.59868466067563</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.116283580642033</v>
+        <v>-1.125646433219885</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.294022883079926</v>
+        <v>-1.402228387691181</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4713566848138839</v>
+        <v>0.3533563772620383</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.7155168958191354</v>
+        <v>0.6674915058433868</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1.069519347226439</v>
+        <v>0.9913733412621468</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.1456876456876444</v>
+        <v>0.04362303412608526</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.1906586410873956</v>
+        <v>-0.2614646210596945</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.3967139198073681</v>
+        <v>-0.4949523479516813</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.091753712972107</v>
+        <v>-1.185922716379352</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.3700675880968305</v>
+        <v>0.2953778097420496</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.5979836769337439</v>
+        <v>0.493168990393599</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.7249774721169331</v>
+        <v>0.6196193716641289</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.1880931582298189</v>
+        <v>0.05680224403928236</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.720780174783421</v>
+        <v>0.6003084110401389</v>
       </c>
     </row>
     <row r="13">
@@ -4372,79 +4372,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.8954432091486808</v>
+        <v>0.7659905063583423</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.6614728624117703</v>
+        <v>0.7204844722576738</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.9781590898450361</v>
+        <v>-0.9350112328403171</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.5822421415458408</v>
+        <v>-0.7258102252357119</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.4932577084875405</v>
+        <v>0.4014372458873936</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.3340641016094281</v>
+        <v>0.3139502152260008</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.5827234859492947</v>
+        <v>-0.4248384188803698</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1491660793986469</v>
+        <v>0.3746588083937468</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.01136694070685706</v>
+        <v>0.1009812923750317</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.693373525834261</v>
+        <v>-1.59868466067563</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.116283580642033</v>
+        <v>-1.125646433219885</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.294022883079926</v>
+        <v>-1.402228387691181</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.4713566848138839</v>
+        <v>0.3533563772620383</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.7155168958191354</v>
+        <v>0.6674915058433868</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.069519347226439</v>
+        <v>0.9913733412621468</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.1456876456876444</v>
+        <v>0.04362303412608526</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1906586410873956</v>
+        <v>-0.2614646210596945</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.3967139198073681</v>
+        <v>-0.4949523479516813</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.091753712972107</v>
+        <v>-1.185922716379352</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.3700675880968305</v>
+        <v>0.2953778097420496</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.5979836769337439</v>
+        <v>0.493168990393599</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.7249774721169331</v>
+        <v>0.6196193716641289</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.1880931582298189</v>
+        <v>0.05680224403928236</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.720780174783421</v>
+        <v>0.6003084110401389</v>
       </c>
     </row>
     <row r="14">
@@ -4454,79 +4454,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.8954432091486808</v>
+        <v>0.7659905063583423</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.6614728624117703</v>
+        <v>0.7204844722576738</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.9781590898450361</v>
+        <v>-0.9350112328403171</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.5822421415458408</v>
+        <v>-0.7258102252357119</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4932577084875405</v>
+        <v>0.4014372458873936</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3340641016094281</v>
+        <v>0.3139502152260008</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.5827234859492947</v>
+        <v>-0.4248384188803698</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.1491660793986469</v>
+        <v>0.3746588083937468</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.01136694070685706</v>
+        <v>0.1009812923750317</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.693373525834261</v>
+        <v>-1.59868466067563</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.116283580642033</v>
+        <v>-1.125646433219885</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.294022883079926</v>
+        <v>-1.402228387691181</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.4713566848138839</v>
+        <v>0.3533563772620383</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.7155168958191354</v>
+        <v>0.6674915058433868</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1.069519347226439</v>
+        <v>0.9913733412621468</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.1456876456876444</v>
+        <v>0.04362303412608526</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.1906586410873956</v>
+        <v>-0.2614646210596945</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.3967139198073681</v>
+        <v>-0.4949523479516813</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.091753712972107</v>
+        <v>-1.185922716379352</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.3700675880968305</v>
+        <v>0.2953778097420496</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.5979836769337439</v>
+        <v>0.493168990393599</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.7249774721169331</v>
+        <v>0.6196193716641289</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.1880931582298189</v>
+        <v>0.05680224403928236</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.720780174783421</v>
+        <v>0.6003084110401389</v>
       </c>
     </row>
     <row r="15">
@@ -4536,79 +4536,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.8954432091486808</v>
+        <v>0.7659905063583423</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.6614728624117703</v>
+        <v>0.7204844722576738</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.9781590898450361</v>
+        <v>-0.9350112328403171</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5822421415458408</v>
+        <v>-0.7258102252357119</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.4932577084875405</v>
+        <v>0.4014372458873936</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3340641016094281</v>
+        <v>0.3139502152260008</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.5827234859492947</v>
+        <v>-0.4248384188803698</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1491660793986469</v>
+        <v>0.3746588083937468</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.01136694070685706</v>
+        <v>0.1009812923750317</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.693373525834261</v>
+        <v>-1.59868466067563</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.116283580642033</v>
+        <v>-1.125646433219885</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.294022883079926</v>
+        <v>-1.402228387691181</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.4713566848138839</v>
+        <v>0.3533563772620383</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.7155168958191354</v>
+        <v>0.6674915058433868</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.069519347226439</v>
+        <v>0.9913733412621468</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.1456876456876444</v>
+        <v>0.04362303412608526</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.1906586410873956</v>
+        <v>-0.2614646210596945</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.3967139198073681</v>
+        <v>-0.4949523479516813</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.091753712972107</v>
+        <v>-1.185922716379352</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.3700675880968305</v>
+        <v>0.2953778097420496</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.5979836769337439</v>
+        <v>0.493168990393599</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.7249774721169331</v>
+        <v>0.6196193716641289</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.1880931582298189</v>
+        <v>0.05680224403928236</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.720780174783421</v>
+        <v>0.6003084110401389</v>
       </c>
     </row>
     <row r="16">
@@ -4618,79 +4618,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1479</v>
+        <v>1488</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.7274324564605053</v>
+        <v>0.699190239157268</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.01057014834091774</v>
+        <v>0.05248180024698001</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.3733203801676126</v>
+        <v>-0.400609095231772</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.220683001760889</v>
+        <v>-1.327012630045331</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.09443837100353392</v>
+        <v>-0.02883506343713549</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1515989248480736</v>
+        <v>-0.03519085346501782</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.2123531155789209</v>
+        <v>-0.1236335996032594</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1154960457286052</v>
+        <v>0.3077244041099405</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.449077378417293</v>
+        <v>-0.4344939418953757</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.49135332381406</v>
+        <v>-1.498283054249924</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.7459132102716595</v>
+        <v>-0.8244416139427742</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.5819152841798712</v>
+        <v>-0.6613546448968251</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.4914700423332405</v>
+        <v>0.4066388755443313</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.7829932790849981</v>
+        <v>0.7345605869969702</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.5297082810995732</v>
+        <v>0.4548206920334437</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.2254324622745614</v>
+        <v>-0.3252569122186557</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.6967315155813267</v>
+        <v>-0.7644827297116024</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.2617611532756499</v>
+        <v>-0.3608141856444931</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.8835154889906036</v>
+        <v>-0.9793139361813772</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.1165284304140854</v>
+        <v>-0.1884657777072363</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.01053559284313366</v>
+        <v>-0.1116697192838103</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.1539948064496599</v>
+        <v>-0.1868322412390953</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.1204799060323936</v>
+        <v>-0.01040205703599639</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.09057885158575374</v>
+        <v>-0.1725410513254602</v>
       </c>
     </row>
     <row r="17">
@@ -4700,79 +4700,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1479</v>
+        <v>1488</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.7274324564605053</v>
+        <v>0.699190239157268</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.01057014834091774</v>
+        <v>0.05248180024698001</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.3733203801676126</v>
+        <v>-0.400609095231772</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.220683001760889</v>
+        <v>-1.327012630045331</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.09443837100353392</v>
+        <v>-0.02883506343713549</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.1515989248480736</v>
+        <v>-0.03519085346501782</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.2123531155789209</v>
+        <v>-0.1236335996032594</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.1154960457286052</v>
+        <v>0.3077244041099405</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.449077378417293</v>
+        <v>-0.4344939418953757</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.49135332381406</v>
+        <v>-1.498283054249924</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.7459132102716595</v>
+        <v>-0.8244416139427742</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.5819152841798712</v>
+        <v>-0.6613546448968251</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.4914700423332405</v>
+        <v>0.4066388755443313</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.7829932790849981</v>
+        <v>0.7345605869969702</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.5297082810995732</v>
+        <v>0.4548206920334437</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.2254324622745614</v>
+        <v>-0.3252569122186557</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.6967315155813267</v>
+        <v>-0.7644827297116024</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.2617611532756499</v>
+        <v>-0.3608141856444931</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.8835154889906036</v>
+        <v>-0.9793139361813772</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.1165284304140854</v>
+        <v>-0.1884657777072363</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.01053559284313366</v>
+        <v>-0.1116697192838103</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.1539948064496599</v>
+        <v>-0.1868322412390953</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.1204799060323936</v>
+        <v>-0.01040205703599639</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.09057885158575374</v>
+        <v>-0.1725410513254602</v>
       </c>
     </row>
     <row r="18">
@@ -4782,79 +4782,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1479</v>
+        <v>1488</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7274324564605053</v>
+        <v>0.699190239157268</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.01057014834091774</v>
+        <v>0.05248180024698001</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.3733203801676126</v>
+        <v>-0.400609095231772</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.220683001760889</v>
+        <v>-1.327012630045331</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.09443837100353392</v>
+        <v>-0.02883506343713549</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.1515989248480736</v>
+        <v>-0.03519085346501782</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.2123531155789209</v>
+        <v>-0.1236335996032594</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.1154960457286052</v>
+        <v>0.3077244041099405</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.449077378417293</v>
+        <v>-0.4344939418953757</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.49135332381406</v>
+        <v>-1.498283054249924</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7459132102716595</v>
+        <v>-0.8244416139427742</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.5819152841798712</v>
+        <v>-0.6613546448968251</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.4914700423332405</v>
+        <v>0.4066388755443313</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.7829932790849981</v>
+        <v>0.7345605869969702</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.5297082810995732</v>
+        <v>0.4548206920334437</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.2254324622745614</v>
+        <v>-0.3252569122186557</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.6967315155813267</v>
+        <v>-0.7644827297116024</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.2617611532756499</v>
+        <v>-0.3608141856444931</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.8835154889906036</v>
+        <v>-0.9793139361813772</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.1165284304140854</v>
+        <v>-0.1884657777072363</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.01053559284313366</v>
+        <v>-0.1116697192838103</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.1539948064496599</v>
+        <v>-0.1868322412390953</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.1204799060323936</v>
+        <v>-0.01040205703599639</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.09057885158575374</v>
+        <v>-0.1725410513254602</v>
       </c>
     </row>
     <row r="19">
@@ -4864,79 +4864,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1479</v>
+        <v>1488</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.7274324564605053</v>
+        <v>0.699190239157268</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.01057014834091774</v>
+        <v>0.05248180024698001</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.3733203801676126</v>
+        <v>-0.400609095231772</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.220683001760889</v>
+        <v>-1.327012630045331</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.09443837100353392</v>
+        <v>-0.02883506343713549</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1515989248480736</v>
+        <v>-0.03519085346501782</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.2123531155789209</v>
+        <v>-0.1236335996032594</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.1154960457286052</v>
+        <v>0.3077244041099405</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.449077378417293</v>
+        <v>-0.4344939418953757</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.49135332381406</v>
+        <v>-1.498283054249924</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.7459132102716595</v>
+        <v>-0.8244416139427742</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.5819152841798712</v>
+        <v>-0.6613546448968251</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.4914700423332405</v>
+        <v>0.4066388755443313</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.7829932790849981</v>
+        <v>0.7345605869969702</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.5297082810995732</v>
+        <v>0.4548206920334437</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.2254324622745614</v>
+        <v>-0.3252569122186557</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.6967315155813267</v>
+        <v>-0.7644827297116024</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.2617611532756499</v>
+        <v>-0.3608141856444931</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.8835154889906036</v>
+        <v>-0.9793139361813772</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.1165284304140854</v>
+        <v>-0.1884657777072363</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.01053559284313366</v>
+        <v>-0.1116697192838103</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.1539948064496599</v>
+        <v>-0.1868322412390953</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.1204799060323936</v>
+        <v>-0.01040205703599639</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.09057885158575374</v>
+        <v>-0.1725410513254602</v>
       </c>
     </row>
     <row r="20">
@@ -4946,79 +4946,79 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1479</v>
+        <v>1488</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7274324564605053</v>
+        <v>0.699190239157268</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.01057014834091774</v>
+        <v>0.05248180024698001</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.3733203801676126</v>
+        <v>-0.400609095231772</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.220683001760889</v>
+        <v>-1.327012630045331</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.09443837100353392</v>
+        <v>-0.02883506343713549</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1515989248480736</v>
+        <v>-0.03519085346501782</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.2123531155789209</v>
+        <v>-0.1236335996032594</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.1154960457286052</v>
+        <v>0.3077244041099405</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.449077378417293</v>
+        <v>-0.4344939418953757</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.49135332381406</v>
+        <v>-1.498283054249924</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7459132102716595</v>
+        <v>-0.8244416139427742</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.5819152841798712</v>
+        <v>-0.6613546448968251</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.4914700423332405</v>
+        <v>0.4066388755443313</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.7829932790849981</v>
+        <v>0.7345605869969702</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.5297082810995732</v>
+        <v>0.4548206920334437</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.2254324622745614</v>
+        <v>-0.3252569122186557</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.6967315155813267</v>
+        <v>-0.7644827297116024</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.2617611532756499</v>
+        <v>-0.3608141856444931</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.8835154889906036</v>
+        <v>-0.9793139361813772</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.1165284304140854</v>
+        <v>-0.1884657777072363</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.01053559284313366</v>
+        <v>-0.1116697192838103</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.1539948064496599</v>
+        <v>-0.1868322412390953</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.1204799060323936</v>
+        <v>-0.01040205703599639</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.09057885158575374</v>
+        <v>-0.1725410513254602</v>
       </c>
     </row>
     <row r="21">
@@ -5028,79 +5028,79 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1966</v>
+        <v>1979</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.7069789735245493</v>
+        <v>0.7014717148828709</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.1333589977271785</v>
+        <v>-0.09692130866629611</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.610811818244521</v>
+        <v>-0.6484511714820442</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.043137192698602</v>
+        <v>-1.163268055469047</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.06595262816887271</v>
+        <v>0.04657971785999848</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2247883553130023</v>
+        <v>-0.1707533925793072</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.005829930332332367</v>
+        <v>0.1190078266957926</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.2840413750854083</v>
+        <v>-0.1859126167128267</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.5971641222487278</v>
+        <v>-0.6115820965606673</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.9141527466134818</v>
+        <v>-0.9546894548902287</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.4083937343842194</v>
+        <v>-0.4525613436167575</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2523690219534487</v>
+        <v>-0.2975072360822253</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.2773402103425369</v>
+        <v>0.2293492448256629</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.4417751419812035</v>
+        <v>0.4142321615780986</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.08820037231942734</v>
+        <v>0.03464964050998987</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.2311182894939208</v>
+        <v>-0.311761923121189</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.3142740051515958</v>
+        <v>-0.3652136913767094</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.1350673041472277</v>
+        <v>-0.1657318179096734</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.7019130230672346</v>
+        <v>-0.7291182855541081</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.4343398870155752</v>
+        <v>-0.4345803824517986</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.1331061069996125</v>
+        <v>-0.2145646319963248</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.04537143108263564</v>
+        <v>0.01345627202109512</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.08707145562147645</v>
+        <v>-0.1976843816595917</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.112039008946482</v>
+        <v>-0.1577010919672475</v>
       </c>
     </row>
     <row r="22">
@@ -5110,79 +5110,79 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1966</v>
+        <v>1979</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.7069789735245493</v>
+        <v>0.7014717148828709</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.1333589977271785</v>
+        <v>-0.09692130866629611</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.610811818244521</v>
+        <v>-0.6484511714820442</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.043137192698602</v>
+        <v>-1.163268055469047</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.06595262816887271</v>
+        <v>0.04657971785999848</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.2247883553130023</v>
+        <v>-0.1707533925793072</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.005829930332332367</v>
+        <v>0.1190078266957926</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.2840413750854083</v>
+        <v>-0.1859126167128267</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.5971641222487278</v>
+        <v>-0.6115820965606673</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.9141527466134818</v>
+        <v>-0.9546894548902287</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.4083937343842194</v>
+        <v>-0.4525613436167575</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2523690219534487</v>
+        <v>-0.2975072360822253</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.2773402103425369</v>
+        <v>0.2293492448256629</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.4417751419812035</v>
+        <v>0.4142321615780986</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.08820037231942734</v>
+        <v>0.03464964050998987</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.2311182894939208</v>
+        <v>-0.311761923121189</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.3142740051515958</v>
+        <v>-0.3652136913767094</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.1350673041472277</v>
+        <v>-0.1657318179096734</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.7019130230672346</v>
+        <v>-0.7291182855541081</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.4343398870155752</v>
+        <v>-0.4345803824517986</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.1331061069996125</v>
+        <v>-0.2145646319963248</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.04537143108263564</v>
+        <v>0.01345627202109512</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.08707145562147645</v>
+        <v>-0.1976843816595917</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.112039008946482</v>
+        <v>-0.1577010919672475</v>
       </c>
     </row>
     <row r="23">
@@ -5192,79 +5192,79 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1966</v>
+        <v>1979</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.7069789735245493</v>
+        <v>0.7014717148828709</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.1333589977271785</v>
+        <v>-0.09692130866629611</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.610811818244521</v>
+        <v>-0.6484511714820442</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.043137192698602</v>
+        <v>-1.163268055469047</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.06595262816887271</v>
+        <v>0.04657971785999848</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2247883553130023</v>
+        <v>-0.1707533925793072</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.005829930332332367</v>
+        <v>0.1190078266957926</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.2840413750854083</v>
+        <v>-0.1859126167128267</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.5971641222487278</v>
+        <v>-0.6115820965606673</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.9141527466134818</v>
+        <v>-0.9546894548902287</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4083937343842194</v>
+        <v>-0.4525613436167575</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.2523690219534487</v>
+        <v>-0.2975072360822253</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.2773402103425369</v>
+        <v>0.2293492448256629</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.4417751419812035</v>
+        <v>0.4142321615780986</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.08820037231942734</v>
+        <v>0.03464964050998987</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.2311182894939208</v>
+        <v>-0.311761923121189</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.3142740051515958</v>
+        <v>-0.3652136913767094</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.1350673041472277</v>
+        <v>-0.1657318179096734</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.7019130230672346</v>
+        <v>-0.7291182855541081</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.4343398870155752</v>
+        <v>-0.4345803824517986</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.1331061069996125</v>
+        <v>-0.2145646319963248</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>0.04537143108263564</v>
+        <v>0.01345627202109512</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.08707145562147645</v>
+        <v>-0.1976843816595917</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.112039008946482</v>
+        <v>-0.1577010919672475</v>
       </c>
     </row>
     <row r="24">
@@ -5274,79 +5274,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1966</v>
+        <v>1979</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.7069789735245493</v>
+        <v>0.7014717148828709</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.1333589977271785</v>
+        <v>-0.09692130866629611</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.610811818244521</v>
+        <v>-0.6484511714820442</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.043137192698602</v>
+        <v>-1.163268055469047</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.06595262816887271</v>
+        <v>0.04657971785999848</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2247883553130023</v>
+        <v>-0.1707533925793072</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.005829930332332367</v>
+        <v>0.1190078266957926</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2840413750854083</v>
+        <v>-0.1859126167128267</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.5971641222487278</v>
+        <v>-0.6115820965606673</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.9141527466134818</v>
+        <v>-0.9546894548902287</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.4083937343842194</v>
+        <v>-0.4525613436167575</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.2523690219534487</v>
+        <v>-0.2975072360822253</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.2773402103425369</v>
+        <v>0.2293492448256629</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.4417751419812035</v>
+        <v>0.4142321615780986</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.08820037231942734</v>
+        <v>0.03464964050998987</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.2311182894939208</v>
+        <v>-0.311761923121189</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.3142740051515958</v>
+        <v>-0.3652136913767094</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.1350673041472277</v>
+        <v>-0.1657318179096734</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.7019130230672346</v>
+        <v>-0.7291182855541081</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.4343398870155752</v>
+        <v>-0.4345803824517986</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.1331061069996125</v>
+        <v>-0.2145646319963248</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.04537143108263564</v>
+        <v>0.01345627202109512</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.08707145562147645</v>
+        <v>-0.1976843816595917</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.112039008946482</v>
+        <v>-0.1577010919672475</v>
       </c>
     </row>
     <row r="25">
@@ -5356,79 +5356,79 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1966</v>
+        <v>1979</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.7069789735245493</v>
+        <v>0.7014717148828709</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.1333589977271785</v>
+        <v>-0.09692130866629611</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.610811818244521</v>
+        <v>-0.6484511714820442</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.043137192698602</v>
+        <v>-1.163268055469047</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.06595262816887271</v>
+        <v>0.04657971785999848</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.2247883553130023</v>
+        <v>-0.1707533925793072</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.005829930332332367</v>
+        <v>0.1190078266957926</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.2840413750854083</v>
+        <v>-0.1859126167128267</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.5971641222487278</v>
+        <v>-0.6115820965606673</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.9141527466134818</v>
+        <v>-0.9546894548902287</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.4083937343842194</v>
+        <v>-0.4525613436167575</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.2523690219534487</v>
+        <v>-0.2975072360822253</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.2773402103425369</v>
+        <v>0.2293492448256629</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.4417751419812035</v>
+        <v>0.4142321615780986</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.08820037231942734</v>
+        <v>0.03464964050998987</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.2311182894939208</v>
+        <v>-0.311761923121189</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.3142740051515958</v>
+        <v>-0.3652136913767094</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.1350673041472277</v>
+        <v>-0.1657318179096734</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.7019130230672346</v>
+        <v>-0.7291182855541081</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.4343398870155752</v>
+        <v>-0.4345803824517986</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.1331061069996125</v>
+        <v>-0.2145646319963248</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.04537143108263564</v>
+        <v>0.01345627202109512</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.08707145562147645</v>
+        <v>-0.1976843816595917</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.112039008946482</v>
+        <v>-0.1577010919672475</v>
       </c>
     </row>
     <row r="26">
@@ -5438,79 +5438,79 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2452</v>
+        <v>2469</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3588373889587118</v>
+        <v>-0.3434315570844362</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.4505023558660568</v>
+        <v>-0.4686140467118491</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4886328270470699</v>
+        <v>-0.5746286318896239</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.7737989267275296</v>
+        <v>-0.8229033240390393</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.08933668512825221</v>
+        <v>0.09203520247744734</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.06600568228981984</v>
+        <v>-0.05090897338375555</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.3685230159631914</v>
+        <v>-0.299336410848241</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4843308878376718</v>
+        <v>-0.4429665316762197</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.2804401330443653</v>
+        <v>-0.3150376219921114</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.3803242680246441</v>
+        <v>-0.4025730662543694</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.2047300116321367</v>
+        <v>-0.2283526576332804</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.2974720084802698</v>
+        <v>-0.3204284386013256</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.1888674405815749</v>
+        <v>0.1629049277690129</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.0733108298624856</v>
+        <v>0.05964239095201407</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.259364607669248</v>
+        <v>-0.2992796677007092</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.3159134058239061</v>
+        <v>-0.3844402953456978</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.262954766015099</v>
+        <v>-0.3029422662355188</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.1400509017008389</v>
+        <v>-0.1289878590367834</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.4701601709154914</v>
+        <v>-0.4569534314138863</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.3407624443791519</v>
+        <v>-0.3400699196693822</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.1662417737087196</v>
+        <v>-0.1955798668611948</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.1605549181589936</v>
+        <v>-0.1897707288974502</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.1714450650328345</v>
+        <v>-0.2295370533356689</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>0.1032439663978266</v>
+        <v>0.03723762359844329</v>
       </c>
     </row>
     <row r="27">
@@ -5520,79 +5520,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2452</v>
+        <v>2469</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.3588373889587118</v>
+        <v>-0.3434315570844362</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4505023558660568</v>
+        <v>-0.4686140467118491</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.4886328270470699</v>
+        <v>-0.5746286318896239</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.7737989267275296</v>
+        <v>-0.8229033240390393</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.08933668512825221</v>
+        <v>0.09203520247744734</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.06600568228981984</v>
+        <v>-0.05090897338375555</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.3685230159631914</v>
+        <v>-0.299336410848241</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.4843308878376718</v>
+        <v>-0.4429665316762197</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2804401330443653</v>
+        <v>-0.3150376219921114</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.3803242680246441</v>
+        <v>-0.4025730662543694</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.2047300116321367</v>
+        <v>-0.2283526576332804</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.2974720084802698</v>
+        <v>-0.3204284386013256</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.1888674405815749</v>
+        <v>0.1629049277690129</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.0733108298624856</v>
+        <v>0.05964239095201407</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.259364607669248</v>
+        <v>-0.2992796677007092</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.3159134058239061</v>
+        <v>-0.3844402953456978</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.262954766015099</v>
+        <v>-0.3029422662355188</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.1400509017008389</v>
+        <v>-0.1289878590367834</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.4701601709154914</v>
+        <v>-0.4569534314138863</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.3407624443791519</v>
+        <v>-0.3400699196693822</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.1662417737087196</v>
+        <v>-0.1955798668611948</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.1605549181589936</v>
+        <v>-0.1897707288974502</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.1714450650328345</v>
+        <v>-0.2295370533356689</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>0.1032439663978266</v>
+        <v>0.03723762359844329</v>
       </c>
     </row>
     <row r="28">
@@ -5602,79 +5602,79 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2452</v>
+        <v>2469</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.3588373889587118</v>
+        <v>-0.3434315570844362</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4505023558660568</v>
+        <v>-0.4686140467118491</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.4886328270470699</v>
+        <v>-0.5746286318896239</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.7737989267275296</v>
+        <v>-0.8229033240390393</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.08933668512825221</v>
+        <v>0.09203520247744734</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.06600568228981984</v>
+        <v>-0.05090897338375555</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.3685230159631914</v>
+        <v>-0.299336410848241</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.4843308878376718</v>
+        <v>-0.4429665316762197</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.2804401330443653</v>
+        <v>-0.3150376219921114</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.3803242680246441</v>
+        <v>-0.4025730662543694</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.2047300116321367</v>
+        <v>-0.2283526576332804</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.2974720084802698</v>
+        <v>-0.3204284386013256</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.1888674405815749</v>
+        <v>0.1629049277690129</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.0733108298624856</v>
+        <v>0.05964239095201407</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.259364607669248</v>
+        <v>-0.2992796677007092</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.3159134058239061</v>
+        <v>-0.3844402953456978</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.262954766015099</v>
+        <v>-0.3029422662355188</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.1400509017008389</v>
+        <v>-0.1289878590367834</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.4701601709154914</v>
+        <v>-0.4569534314138863</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3407624443791519</v>
+        <v>-0.3400699196693822</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.1662417737087196</v>
+        <v>-0.1955798668611948</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.1605549181589936</v>
+        <v>-0.1897707288974502</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.1714450650328345</v>
+        <v>-0.2295370533356689</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>0.1032439663978266</v>
+        <v>0.03723762359844329</v>
       </c>
     </row>
     <row r="29">
@@ -5684,79 +5684,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2452</v>
+        <v>2469</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.3588373889587118</v>
+        <v>-0.3434315570844362</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.4505023558660568</v>
+        <v>-0.4686140467118491</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.4886328270470699</v>
+        <v>-0.5746286318896239</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.7737989267275296</v>
+        <v>-0.8229033240390393</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.08933668512825221</v>
+        <v>0.09203520247744734</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.06600568228981984</v>
+        <v>-0.05090897338375555</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.3685230159631914</v>
+        <v>-0.299336410848241</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.4843308878376718</v>
+        <v>-0.4429665316762197</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.2804401330443653</v>
+        <v>-0.3150376219921114</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.3803242680246441</v>
+        <v>-0.4025730662543694</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.2047300116321367</v>
+        <v>-0.2283526576332804</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.2974720084802698</v>
+        <v>-0.3204284386013256</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.1888674405815749</v>
+        <v>0.1629049277690129</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.0733108298624856</v>
+        <v>0.05964239095201407</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.259364607669248</v>
+        <v>-0.2992796677007092</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.3159134058239061</v>
+        <v>-0.3844402953456978</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.262954766015099</v>
+        <v>-0.3029422662355188</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.1400509017008389</v>
+        <v>-0.1289878590367834</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.4701601709154914</v>
+        <v>-0.4569534314138863</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.3407624443791519</v>
+        <v>-0.3400699196693822</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.1662417737087196</v>
+        <v>-0.1955798668611948</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.1605549181589936</v>
+        <v>-0.1897707288974502</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.1714450650328345</v>
+        <v>-0.2295370533356689</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.1032439663978266</v>
+        <v>0.03723762359844329</v>
       </c>
     </row>
     <row r="30">
@@ -5766,79 +5766,79 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2452</v>
+        <v>2469</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.3588373889587118</v>
+        <v>-0.3434315570844362</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.4505023558660568</v>
+        <v>-0.4686140467118491</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.4886328270470699</v>
+        <v>-0.5746286318896239</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.7737989267275296</v>
+        <v>-0.8229033240390393</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.08933668512825221</v>
+        <v>0.09203520247744734</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.06600568228981984</v>
+        <v>-0.05090897338375555</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.3685230159631914</v>
+        <v>-0.299336410848241</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.4843308878376718</v>
+        <v>-0.4429665316762197</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.2804401330443653</v>
+        <v>-0.3150376219921114</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.3803242680246441</v>
+        <v>-0.4025730662543694</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.2047300116321367</v>
+        <v>-0.2283526576332804</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.2974720084802698</v>
+        <v>-0.3204284386013256</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.1888674405815749</v>
+        <v>0.1629049277690129</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.0733108298624856</v>
+        <v>0.05964239095201407</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.259364607669248</v>
+        <v>-0.2992796677007092</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.3159134058239061</v>
+        <v>-0.3844402953456978</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.262954766015099</v>
+        <v>-0.3029422662355188</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.1400509017008389</v>
+        <v>-0.1289878590367834</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.4701601709154914</v>
+        <v>-0.4569534314138863</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.3407624443791519</v>
+        <v>-0.3400699196693822</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.1662417737087196</v>
+        <v>-0.1955798668611948</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.1605549181589936</v>
+        <v>-0.1897707288974502</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.1714450650328345</v>
+        <v>-0.2295370533356689</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.1032439663978266</v>
+        <v>0.03723762359844329</v>
       </c>
     </row>
     <row r="31">
@@ -5848,79 +5848,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2938</v>
+        <v>2959</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.192571251363006</v>
+        <v>-0.1690114209605511</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.137274233053347</v>
+        <v>-0.1619385335928456</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2377295643310404</v>
+        <v>-0.2565296475669783</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.3228744760253974</v>
+        <v>-0.3264900795680319</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.03727402316200568</v>
+        <v>0.05519855000824236</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.09526549291604169</v>
+        <v>-0.0716720179833743</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.4078035549318031</v>
+        <v>-0.3771197946356608</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.2117602571374491</v>
+        <v>-0.2111354280880064</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.05240188958178749</v>
+        <v>0.03679453187408654</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.1248064996401155</v>
+        <v>-0.1342946198661323</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.1023805626698362</v>
+        <v>-0.1120972871406138</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.0223509397661914</v>
+        <v>-0.03262062014405842</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.06182983311674661</v>
+        <v>0.05110387485783008</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.03730515617752417</v>
+        <v>-0.04253203275931128</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1523391530113116</v>
+        <v>-0.1854211635489946</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.148814117404946</v>
+        <v>-0.1772572034694164</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.1267119327613955</v>
+        <v>-0.126387717819</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.1094062206213451</v>
+        <v>-0.1044175059713197</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.2811426273959015</v>
+        <v>-0.274989686543222</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.1421678066144878</v>
+        <v>-0.1418488810774861</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.1883998419910711</v>
+        <v>-0.2166636729393971</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.06016417074710745</v>
+        <v>-0.05541957550934029</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>0.06455346299326692</v>
+        <v>0.005581668625154634</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.04308274431713954</v>
+        <v>-0.001361998535898579</v>
       </c>
     </row>
     <row r="32">
@@ -5930,79 +5930,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2938</v>
+        <v>2959</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.192571251363006</v>
+        <v>-0.1690114209605511</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.137274233053347</v>
+        <v>-0.1619385335928456</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2377295643310404</v>
+        <v>-0.2565296475669783</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3228744760253974</v>
+        <v>-0.3264900795680319</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.03727402316200568</v>
+        <v>0.05519855000824236</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.09526549291604169</v>
+        <v>-0.0716720179833743</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4078035549318031</v>
+        <v>-0.3771197946356608</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.2117602571374491</v>
+        <v>-0.2111354280880064</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.05240188958178749</v>
+        <v>0.03679453187408654</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1248064996401155</v>
+        <v>-0.1342946198661323</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1023805626698362</v>
+        <v>-0.1120972871406138</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.0223509397661914</v>
+        <v>-0.03262062014405842</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.06182983311674661</v>
+        <v>0.05110387485783008</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.03730515617752417</v>
+        <v>-0.04253203275931128</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.1523391530113116</v>
+        <v>-0.1854211635489946</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.148814117404946</v>
+        <v>-0.1772572034694164</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.1267119327613955</v>
+        <v>-0.126387717819</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.1094062206213451</v>
+        <v>-0.1044175059713197</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.2811426273959015</v>
+        <v>-0.274989686543222</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.1421678066144878</v>
+        <v>-0.1418488810774861</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.1883998419910711</v>
+        <v>-0.2166636729393971</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.06016417074710745</v>
+        <v>-0.05541957550934029</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>0.06455346299326692</v>
+        <v>0.005581668625154634</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.04308274431713954</v>
+        <v>-0.001361998535898579</v>
       </c>
     </row>
     <row r="33">
@@ -6012,79 +6012,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2938</v>
+        <v>2959</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.192571251363006</v>
+        <v>-0.1690114209605511</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.137274233053347</v>
+        <v>-0.1619385335928456</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2377295643310404</v>
+        <v>-0.2565296475669783</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3228744760253974</v>
+        <v>-0.3264900795680319</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.03727402316200568</v>
+        <v>0.05519855000824236</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.09526549291604169</v>
+        <v>-0.0716720179833743</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.4078035549318031</v>
+        <v>-0.3771197946356608</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.2117602571374491</v>
+        <v>-0.2111354280880064</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.05240188958178749</v>
+        <v>0.03679453187408654</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1248064996401155</v>
+        <v>-0.1342946198661323</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1023805626698362</v>
+        <v>-0.1120972871406138</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.0223509397661914</v>
+        <v>-0.03262062014405842</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.06182983311674661</v>
+        <v>0.05110387485783008</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.03730515617752417</v>
+        <v>-0.04253203275931128</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.1523391530113116</v>
+        <v>-0.1854211635489946</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.148814117404946</v>
+        <v>-0.1772572034694164</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.1267119327613955</v>
+        <v>-0.126387717819</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.1094062206213451</v>
+        <v>-0.1044175059713197</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.2811426273959015</v>
+        <v>-0.274989686543222</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.1421678066144878</v>
+        <v>-0.1418488810774861</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.1883998419910711</v>
+        <v>-0.2166636729393971</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.06016417074710745</v>
+        <v>-0.05541957550934029</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>0.06455346299326692</v>
+        <v>0.005581668625154634</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.04308274431713954</v>
+        <v>-0.001361998535898579</v>
       </c>
     </row>
     <row r="34">
@@ -6094,79 +6094,79 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2938</v>
+        <v>2959</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.192571251363006</v>
+        <v>-0.1690114209605511</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.137274233053347</v>
+        <v>-0.1619385335928456</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2377295643310404</v>
+        <v>-0.2565296475669783</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.3228744760253974</v>
+        <v>-0.3264900795680319</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.03727402316200568</v>
+        <v>0.05519855000824236</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.09526549291604169</v>
+        <v>-0.0716720179833743</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.4078035549318031</v>
+        <v>-0.3771197946356608</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.2117602571374491</v>
+        <v>-0.2111354280880064</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.05240188958178749</v>
+        <v>0.03679453187408654</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1248064996401155</v>
+        <v>-0.1342946198661323</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1023805626698362</v>
+        <v>-0.1120972871406138</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.0223509397661914</v>
+        <v>-0.03262062014405842</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.06182983311674661</v>
+        <v>0.05110387485783008</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.03730515617752417</v>
+        <v>-0.04253203275931128</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.1523391530113116</v>
+        <v>-0.1854211635489946</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.148814117404946</v>
+        <v>-0.1772572034694164</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.1267119327613955</v>
+        <v>-0.126387717819</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.1094062206213451</v>
+        <v>-0.1044175059713197</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.2811426273959015</v>
+        <v>-0.274989686543222</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.1421678066144878</v>
+        <v>-0.1418488810774861</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.1883998419910711</v>
+        <v>-0.2166636729393971</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.06016417074710745</v>
+        <v>-0.05541957550934029</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>0.06455346299326692</v>
+        <v>0.005581668625154634</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>0.04308274431713954</v>
+        <v>-0.001361998535898579</v>
       </c>
     </row>
     <row r="35">
@@ -6176,79 +6176,79 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2938</v>
+        <v>2959</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.192571251363006</v>
+        <v>-0.1690114209605511</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.137274233053347</v>
+        <v>-0.1619385335928456</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2377295643310404</v>
+        <v>-0.2565296475669783</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.3228744760253974</v>
+        <v>-0.3264900795680319</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.03727402316200568</v>
+        <v>0.05519855000824236</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.09526549291604169</v>
+        <v>-0.0716720179833743</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4078035549318031</v>
+        <v>-0.3771197946356608</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.2117602571374491</v>
+        <v>-0.2111354280880064</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.05240188958178749</v>
+        <v>0.03679453187408654</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1248064996401155</v>
+        <v>-0.1342946198661323</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1023805626698362</v>
+        <v>-0.1120972871406138</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.0223509397661914</v>
+        <v>-0.03262062014405842</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.06182983311674661</v>
+        <v>0.05110387485783008</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.03730515617752417</v>
+        <v>-0.04253203275931128</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.1523391530113116</v>
+        <v>-0.1854211635489946</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.148814117404946</v>
+        <v>-0.1772572034694164</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.1267119327613955</v>
+        <v>-0.126387717819</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.1094062206213451</v>
+        <v>-0.1044175059713197</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.2811426273959015</v>
+        <v>-0.274989686543222</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.1421678066144878</v>
+        <v>-0.1418488810774861</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.1883998419910711</v>
+        <v>-0.2166636729393971</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.06016417074710745</v>
+        <v>-0.05541957550934029</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>0.06455346299326692</v>
+        <v>0.005581668625154634</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>0.04308274431713954</v>
+        <v>-0.001361998535898579</v>
       </c>
     </row>
   </sheetData>
